--- a/trades_taken.xlsx
+++ b/trades_taken.xlsx
@@ -548,7 +548,7 @@
         <v>5.749174382292647</v>
       </c>
       <c r="F2" t="n">
-        <v>1.141826279098585</v>
+        <v>1.141947091075164</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -591,7 +591,7 @@
         <v>5.773188699286039</v>
       </c>
       <c r="F3" t="n">
-        <v>1.134682625773983</v>
+        <v>1.134803942382518</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -644,7 +644,7 @@
         <v>5.78387729560523</v>
       </c>
       <c r="F4" t="n">
-        <v>1.105323031907443</v>
+        <v>1.105444573123957</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -697,7 +697,7 @@
         <v>5.793449133348831</v>
       </c>
       <c r="F5" t="n">
-        <v>1.097541426021955</v>
+        <v>1.097663168379113</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -750,7 +750,7 @@
         <v>5.803412368221555</v>
       </c>
       <c r="F6" t="n">
-        <v>1.090887357480231</v>
+        <v>1.091009309202772</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -803,7 +803,7 @@
         <v>5.815721008562775</v>
       </c>
       <c r="F7" t="n">
-        <v>1.086825520202334</v>
+        <v>1.08694773057613</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -856,7 +856,7 @@
         <v>5.815334021863411</v>
       </c>
       <c r="F8" t="n">
-        <v>1.072627019158087</v>
+        <v>1.072749221399825</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -909,7 +909,7 @@
         <v>5.806180843814804</v>
       </c>
       <c r="F9" t="n">
-        <v>1.100262632144622</v>
+        <v>1.100384642043344</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -962,7 +962,7 @@
         <v>5.797791852433679</v>
       </c>
       <c r="F10" t="n">
-        <v>1.101836173351318</v>
+        <v>1.101958006965488</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -1015,7 +1015,7 @@
         <v>5.773250764797821</v>
       </c>
       <c r="F11" t="n">
-        <v>1.074486443359815</v>
+        <v>1.07460776127258</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
         <v>5.792870686585944</v>
       </c>
       <c r="F12" t="n">
-        <v>1.089587472870435</v>
+        <v>1.089709203072231</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -1121,7 +1121,7 @@
         <v>5.799426812342785</v>
       </c>
       <c r="F13" t="n">
-        <v>1.093181360634961</v>
+        <v>1.093303228605845</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1174,7 +1174,7 @@
         <v>5.791499330208546</v>
       </c>
       <c r="F14" t="n">
-        <v>1.114014641503429</v>
+        <v>1.114136342887822</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1227,7 +1227,7 @@
         <v>5.807622181149471</v>
       </c>
       <c r="F15" t="n">
-        <v>1.096131873786599</v>
+        <v>1.09625391397329</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
         <v>5.811485489879658</v>
       </c>
       <c r="F16" t="n">
-        <v>1.104317652985041</v>
+        <v>1.104439774354512</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -1333,7 +1333,7 @@
         <v>5.815840058266167</v>
       </c>
       <c r="F17" t="n">
-        <v>1.11700838061204</v>
+        <v>1.117130593487522</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1386,7 +1386,7 @@
         <v>5.822484503418294</v>
       </c>
       <c r="F18" t="n">
-        <v>1.117438125333774</v>
+        <v>1.11756047783427</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1439,7 +1439,7 @@
         <v>5.821745073183263</v>
       </c>
       <c r="F19" t="n">
-        <v>1.110769841461688</v>
+        <v>1.110892178423948</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1492,7 +1492,7 @@
         <v>5.838439218027872</v>
       </c>
       <c r="F20" t="n">
-        <v>1.069589211322751</v>
+        <v>1.069711899092362</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1545,16 +1545,16 @@
         <v>5.826791450769824</v>
       </c>
       <c r="F21" t="n">
-        <v>1.049070440827043</v>
+        <v>1.049192883832851</v>
       </c>
       <c r="G21" t="n">
-        <v>1.098370375491807</v>
+        <v>1.098492297099277</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02201289725452328</v>
+        <v>0.02201266124285643</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.239593184610612</v>
+        <v>-2.239593510413244</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1604,16 +1604,16 @@
         <v>5.806961871948709</v>
       </c>
       <c r="F22" t="n">
-        <v>1.028477897619893</v>
+        <v>1.02859992393098</v>
       </c>
       <c r="G22" t="n">
-        <v>1.092702956417872</v>
+        <v>1.092824938742068</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02466719043036316</v>
+        <v>0.02466708176955401</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.603663314607727</v>
+        <v>-2.603673000766515</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -1663,16 +1663,16 @@
         <v>5.801572597986273</v>
       </c>
       <c r="F23" t="n">
-        <v>1.018961128262691</v>
+        <v>1.019083041324676</v>
       </c>
       <c r="G23" t="n">
-        <v>1.086916881542308</v>
+        <v>1.087038893689176</v>
       </c>
       <c r="H23" t="n">
-        <v>0.02768899336895551</v>
+        <v>0.0276889659559465</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.454251491706717</v>
+        <v>-2.454257499995431</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1722,16 +1722,16 @@
         <v>5.775917931798511</v>
       </c>
       <c r="F24" t="n">
-        <v>1.112982141440127</v>
+        <v>1.113103515400194</v>
       </c>
       <c r="G24" t="n">
-        <v>1.087299837018942</v>
+        <v>1.087421840802988</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02800808626306863</v>
+        <v>0.02800804431260939</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9169603442363619</v>
+        <v>0.9169392304068992</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1781,16 +1781,16 @@
         <v>5.780429907926294</v>
       </c>
       <c r="F25" t="n">
-        <v>1.134437707914076</v>
+        <v>1.13455917668789</v>
       </c>
       <c r="G25" t="n">
-        <v>1.089144651113548</v>
+        <v>1.089266641218427</v>
       </c>
       <c r="H25" t="n">
-        <v>0.02987132666042008</v>
+        <v>0.02987124849863178</v>
       </c>
       <c r="I25" t="n">
-        <v>1.51627201949963</v>
+        <v>1.516258534407675</v>
       </c>
       <c r="J25" t="n">
         <v>-1</v>
@@ -1840,16 +1840,16 @@
         <v>5.762572732764129</v>
       </c>
       <c r="F26" t="n">
-        <v>1.139215016486785</v>
+        <v>1.139336110013565</v>
       </c>
       <c r="G26" t="n">
-        <v>1.091561034063875</v>
+        <v>1.091682981258966</v>
       </c>
       <c r="H26" t="n">
-        <v>0.0319051664719824</v>
+        <v>0.03190502276937025</v>
       </c>
       <c r="I26" t="n">
-        <v>1.493613345185255</v>
+        <v>1.493593315982446</v>
       </c>
       <c r="J26" t="n">
         <v>-1</v>
@@ -1899,16 +1899,16 @@
         <v>5.738363354184461</v>
       </c>
       <c r="F27" t="n">
-        <v>1.164412077401906</v>
+        <v>1.164532662197749</v>
       </c>
       <c r="G27" t="n">
-        <v>1.095440361923854</v>
+        <v>1.095562227840047</v>
       </c>
       <c r="H27" t="n">
-        <v>0.0357805585519463</v>
+        <v>0.03578029552809846</v>
       </c>
       <c r="I27" t="n">
-        <v>1.927631045164332</v>
+        <v>1.927609410144153</v>
       </c>
       <c r="J27" t="n">
         <v>-1</v>
@@ -1958,16 +1958,16 @@
         <v>5.732040520720335</v>
       </c>
       <c r="F28" t="n">
-        <v>1.152409951745634</v>
+        <v>1.152530403674744</v>
       </c>
       <c r="G28" t="n">
-        <v>1.099429508553232</v>
+        <v>1.099551286953793</v>
       </c>
       <c r="H28" t="n">
-        <v>0.0375089735054342</v>
+        <v>0.03750863013418261</v>
       </c>
       <c r="I28" t="n">
-        <v>1.412473822690101</v>
+        <v>1.412451388691732</v>
       </c>
       <c r="J28" t="n">
         <v>-1</v>
@@ -2017,16 +2017,16 @@
         <v>5.721368826915722</v>
       </c>
       <c r="F29" t="n">
-        <v>1.137660216715829</v>
+        <v>1.137780444392145</v>
       </c>
       <c r="G29" t="n">
-        <v>1.101299387781792</v>
+        <v>1.101421077071233</v>
       </c>
       <c r="H29" t="n">
-        <v>0.03847248008936358</v>
+        <v>0.0384720685093613</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9451126844325674</v>
+        <v>0.9450848038509821</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2076,16 +2076,16 @@
         <v>5.70919231456057</v>
       </c>
       <c r="F30" t="n">
-        <v>1.15806762630886</v>
+        <v>1.158187598110431</v>
       </c>
       <c r="G30" t="n">
-        <v>1.104110960429669</v>
+        <v>1.10423255662848</v>
       </c>
       <c r="H30" t="n">
-        <v>0.04051429163818596</v>
+        <v>0.04051378084160917</v>
       </c>
       <c r="I30" t="n">
-        <v>1.33179339184929</v>
+        <v>1.331770088131027</v>
       </c>
       <c r="J30" t="n">
         <v>-1</v>
@@ -2135,16 +2135,16 @@
         <v>5.713520469255783</v>
       </c>
       <c r="F31" t="n">
-        <v>1.171130879586729</v>
+        <v>1.171250942339261</v>
       </c>
       <c r="G31" t="n">
-        <v>1.108943182241015</v>
+        <v>1.109064715681815</v>
       </c>
       <c r="H31" t="n">
-        <v>0.04250931719013069</v>
+        <v>0.04250870042499809</v>
       </c>
       <c r="I31" t="n">
-        <v>1.462919224685941</v>
+        <v>1.462905853053935</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -2194,16 +2194,16 @@
         <v>5.711936800350696</v>
       </c>
       <c r="F32" t="n">
-        <v>1.171831704095611</v>
+        <v>1.171951733569247</v>
       </c>
       <c r="G32" t="n">
-        <v>1.113055393802273</v>
+        <v>1.113176842206665</v>
       </c>
       <c r="H32" t="n">
-        <v>0.04447111181121043</v>
+        <v>0.04447042310042733</v>
       </c>
       <c r="I32" t="n">
-        <v>1.321673956406944</v>
+        <v>1.321662517800895</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -2253,16 +2253,16 @@
         <v>5.75120839641801</v>
       </c>
       <c r="F33" t="n">
-        <v>1.154064544717499</v>
+        <v>1.154185399436435</v>
       </c>
       <c r="G33" t="n">
-        <v>1.1160995530064</v>
+        <v>1.116220950748195</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04511817878931619</v>
+        <v>0.04511748488006197</v>
       </c>
       <c r="I33" t="n">
-        <v>0.841456652946471</v>
+        <v>0.8414575588413939</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2312,16 +2312,16 @@
         <v>5.740066355466205</v>
       </c>
       <c r="F34" t="n">
-        <v>1.171062320619905</v>
+        <v>1.171182941202269</v>
       </c>
       <c r="G34" t="n">
-        <v>1.118951936962224</v>
+        <v>1.119073280663917</v>
       </c>
       <c r="H34" t="n">
-        <v>0.04675309625049977</v>
+        <v>0.04675238270422814</v>
       </c>
       <c r="I34" t="n">
-        <v>1.114586793962845</v>
+        <v>1.11458833805361</v>
       </c>
       <c r="J34" t="n">
         <v>-1</v>
@@ -2371,16 +2371,16 @@
         <v>5.738170534486693</v>
       </c>
       <c r="F35" t="n">
-        <v>1.179174696136368</v>
+        <v>1.179295276880336</v>
       </c>
       <c r="G35" t="n">
-        <v>1.123104078079713</v>
+        <v>1.123225348809269</v>
       </c>
       <c r="H35" t="n">
-        <v>0.04828228840190949</v>
+        <v>0.04828157129980546</v>
       </c>
       <c r="I35" t="n">
-        <v>1.161308212856741</v>
+        <v>1.161311170320025</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2430,16 +2430,16 @@
         <v>5.744582886912311</v>
       </c>
       <c r="F36" t="n">
-        <v>1.188568094453422</v>
+        <v>1.188688809945255</v>
       </c>
       <c r="G36" t="n">
-        <v>1.127316600153132</v>
+        <v>1.127437800588806</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05019441619225083</v>
+        <v>0.05019371126094478</v>
       </c>
       <c r="I36" t="n">
-        <v>1.220285022654504</v>
+        <v>1.220292499154316</v>
       </c>
       <c r="J36" t="n">
         <v>-1</v>
@@ -2489,16 +2489,16 @@
         <v>5.726783927032285</v>
       </c>
       <c r="F37" t="n">
-        <v>1.145122201880307</v>
+        <v>1.145242543348432</v>
       </c>
       <c r="G37" t="n">
-        <v>1.128722291216545</v>
+        <v>1.128843398081852</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0502841241222951</v>
+        <v>0.0502834181170008</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3261449006027446</v>
+        <v>0.3261342581847064</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2548,16 +2548,16 @@
         <v>5.740932893433766</v>
       </c>
       <c r="F38" t="n">
-        <v>1.092519733490692</v>
+        <v>1.092640372282307</v>
       </c>
       <c r="G38" t="n">
-        <v>1.127476371624391</v>
+        <v>1.127597392804254</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05088356994148131</v>
+        <v>0.05088290211111998</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6869926417093202</v>
+        <v>-0.6870091734470395</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2607,16 +2607,16 @@
         <v>5.723982150556365</v>
       </c>
       <c r="F39" t="n">
-        <v>1.133994639076319</v>
+        <v>1.134114921668485</v>
       </c>
       <c r="G39" t="n">
-        <v>1.128637611505122</v>
+        <v>1.12875852996648</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05074706432218951</v>
+        <v>0.05074641497452159</v>
       </c>
       <c r="I39" t="n">
-        <v>0.105563299921859</v>
+        <v>0.1055521203752783</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2666,16 +2666,16 @@
         <v>5.714344279418622</v>
       </c>
       <c r="F40" t="n">
-        <v>1.127443955042871</v>
+        <v>1.12756403510678</v>
       </c>
       <c r="G40" t="n">
-        <v>1.131530348691128</v>
+        <v>1.131651136767202</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04881618524315948</v>
+        <v>0.04881563206320536</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.08370981116001842</v>
+        <v>-0.08372526356166977</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2725,16 +2725,16 @@
         <v>5.712861012783621</v>
       </c>
       <c r="F41" t="n">
-        <v>1.144969116212413</v>
+        <v>1.14508916510726</v>
       </c>
       <c r="G41" t="n">
-        <v>1.136325282460397</v>
+        <v>1.136445950830922</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04483802143781376</v>
+        <v>0.04483758117768515</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1927791074368443</v>
+        <v>0.1927671843422123</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2784,16 +2784,16 @@
         <v>5.705410786907837</v>
       </c>
       <c r="F42" t="n">
-        <v>1.151905981487951</v>
+        <v>1.152025873825273</v>
       </c>
       <c r="G42" t="n">
-        <v>1.1424966866538</v>
+        <v>1.142617248325636</v>
       </c>
       <c r="H42" t="n">
-        <v>0.03702665493197799</v>
+        <v>0.03702633149706917</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2541221952519609</v>
+        <v>0.2541063378201784</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2843,16 +2843,16 @@
         <v>5.697536098237152</v>
       </c>
       <c r="F43" t="n">
-        <v>1.126936811753264</v>
+        <v>1.127056538613487</v>
       </c>
       <c r="G43" t="n">
-        <v>1.147895470828328</v>
+        <v>1.148015923190077</v>
       </c>
       <c r="H43" t="n">
-        <v>0.02344829523849202</v>
+        <v>0.02344821487991332</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.8938244278270175</v>
+        <v>-0.8938584316090068</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2902,16 +2902,16 @@
         <v>5.724163671495992</v>
       </c>
       <c r="F44" t="n">
-        <v>1.134796653971521</v>
+        <v>1.134916940378131</v>
       </c>
       <c r="G44" t="n">
-        <v>1.148986196454898</v>
+        <v>1.149106594438974</v>
       </c>
       <c r="H44" t="n">
-        <v>0.02221364354159552</v>
+        <v>0.02221364291268626</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6387760052423042</v>
+        <v>-0.6387810462524249</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2961,16 +2961,16 @@
         <v>5.726380928450948</v>
       </c>
       <c r="F45" t="n">
-        <v>1.144759585041945</v>
+        <v>1.14487991804154</v>
       </c>
       <c r="G45" t="n">
-        <v>1.149502290311291</v>
+        <v>1.149622631506656</v>
       </c>
       <c r="H45" t="n">
-        <v>0.02197648491637061</v>
+        <v>0.02197652364951244</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2158081825821639</v>
+        <v>-0.2158081751579287</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3020,16 +3020,16 @@
         <v>5.731772886030789</v>
       </c>
       <c r="F46" t="n">
-        <v>1.147774604564161</v>
+        <v>1.147895050869251</v>
       </c>
       <c r="G46" t="n">
-        <v>1.14993026971516</v>
+        <v>1.150050578549441</v>
       </c>
       <c r="H46" t="n">
-        <v>0.02184857632867353</v>
+        <v>0.02184863416137732</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.09866387258238934</v>
+        <v>-0.0986573194584439</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3079,16 +3079,16 @@
         <v>5.714949142745352</v>
       </c>
       <c r="F47" t="n">
-        <v>1.144084193628695</v>
+        <v>1.144204286403078</v>
       </c>
       <c r="G47" t="n">
-        <v>1.1489138755265</v>
+        <v>1.149034159759707</v>
       </c>
       <c r="H47" t="n">
-        <v>0.02161095990586548</v>
+        <v>0.02161101049974041</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2234829882079531</v>
+        <v>-0.2234913243268649</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3138,16 +3138,16 @@
         <v>5.710756593323133</v>
       </c>
       <c r="F48" t="n">
-        <v>1.131160174610352</v>
+        <v>1.131280179283359</v>
       </c>
       <c r="G48" t="n">
-        <v>1.147851386669736</v>
+        <v>1.147971648540138</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02194974147897231</v>
+        <v>0.02194980064767979</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7604286399169319</v>
+        <v>-0.7604383076045458</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3197,16 +3197,16 @@
         <v>5.721549023996647</v>
       </c>
       <c r="F49" t="n">
-        <v>1.139826493463808</v>
+        <v>1.139946724926748</v>
       </c>
       <c r="G49" t="n">
-        <v>1.147959700507135</v>
+        <v>1.148079962566868</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02190209818964759</v>
+        <v>0.02190215723505423</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3713437394400494</v>
+        <v>-0.3713441353211905</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3256,16 +3256,16 @@
         <v>5.738938545760967</v>
       </c>
       <c r="F50" t="n">
-        <v>1.120391751973521</v>
+        <v>1.120512348856322</v>
       </c>
       <c r="G50" t="n">
-        <v>1.146075906790368</v>
+        <v>1.146196200104163</v>
       </c>
       <c r="H50" t="n">
-        <v>0.02259620862942144</v>
+        <v>0.02259625393793602</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.1366577127193</v>
+        <v>-1.136641999084675</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -3315,16 +3315,16 @@
         <v>5.728495630575953</v>
       </c>
       <c r="F51" t="n">
-        <v>1.119374361197232</v>
+        <v>1.119494738634745</v>
       </c>
       <c r="G51" t="n">
-        <v>1.143488080870893</v>
+        <v>1.143608389918937</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02253940206033145</v>
+        <v>0.02253945762851689</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.069847354828479</v>
+        <v>-1.069841683044033</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -3374,16 +3374,16 @@
         <v>5.726673971164641</v>
       </c>
       <c r="F52" t="n">
-        <v>1.110418153869186</v>
+        <v>1.11053849302672</v>
       </c>
       <c r="G52" t="n">
-        <v>1.140417403359572</v>
+        <v>1.140537727891811</v>
       </c>
       <c r="H52" t="n">
-        <v>0.02265780468105381</v>
+        <v>0.02265787826162289</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.324013950719179</v>
+        <v>-1.324009005552044</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -3433,16 +3433,16 @@
         <v>5.706513118053733</v>
       </c>
       <c r="F53" t="n">
-        <v>1.091389717338871</v>
+        <v>1.091509632840355</v>
       </c>
       <c r="G53" t="n">
-        <v>1.13728366199064</v>
+        <v>1.137403939562007</v>
       </c>
       <c r="H53" t="n">
-        <v>0.0248947352035948</v>
+        <v>0.02489482304977883</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.843520096777005</v>
+        <v>-1.843528135543815</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -3492,16 +3492,16 @@
         <v>5.710028592673332</v>
       </c>
       <c r="F54" t="n">
-        <v>1.105769686989136</v>
+        <v>1.105889676364086</v>
       </c>
       <c r="G54" t="n">
-        <v>1.134019030309102</v>
+        <v>1.134139276320097</v>
       </c>
       <c r="H54" t="n">
-        <v>0.02451013261744044</v>
+        <v>0.02451021203965659</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.152557750742826</v>
+        <v>-1.152564486602757</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -3551,16 +3551,16 @@
         <v>5.670799921537744</v>
       </c>
       <c r="F55" t="n">
-        <v>1.13116442567198</v>
+        <v>1.131283590703644</v>
       </c>
       <c r="G55" t="n">
-        <v>1.131618516785882</v>
+        <v>1.131738692011263</v>
       </c>
       <c r="H55" t="n">
-        <v>0.02208601692115957</v>
+        <v>0.02208606829704957</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.02056011799333949</v>
+        <v>-0.02060580912355634</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3610,16 +3610,16 @@
         <v>5.672485518208908</v>
       </c>
       <c r="F56" t="n">
-        <v>1.149633810870154</v>
+        <v>1.149753011322602</v>
       </c>
       <c r="G56" t="n">
-        <v>1.129671802606719</v>
+        <v>1.12979190208013</v>
       </c>
       <c r="H56" t="n">
-        <v>0.01817104873131073</v>
+        <v>0.01817096265221098</v>
       </c>
       <c r="I56" t="n">
-        <v>1.098561153987668</v>
+        <v>1.098516882375687</v>
       </c>
       <c r="J56" t="n">
         <v>-1</v>
@@ -3669,16 +3669,16 @@
         <v>5.63747285479881</v>
       </c>
       <c r="F57" t="n">
-        <v>1.132007756532976</v>
+        <v>1.132126221236463</v>
       </c>
       <c r="G57" t="n">
-        <v>1.129016080339353</v>
+        <v>1.129136085974532</v>
       </c>
       <c r="H57" t="n">
-        <v>0.01781734169597524</v>
+        <v>0.01781722795127691</v>
       </c>
       <c r="I57" t="n">
-        <v>0.16790811135978</v>
+        <v>0.1678226977904937</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3728,16 +3728,16 @@
         <v>5.613771107697508</v>
       </c>
       <c r="F58" t="n">
-        <v>1.126903223657087</v>
+        <v>1.127021190296901</v>
       </c>
       <c r="G58" t="n">
-        <v>1.130735254847672</v>
+        <v>1.130855126875262</v>
       </c>
       <c r="H58" t="n">
-        <v>0.01563576407735688</v>
+        <v>0.01563574221715024</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2450811595535944</v>
+        <v>-0.2452033632375522</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3787,16 +3787,16 @@
         <v>5.610704481843535</v>
       </c>
       <c r="F59" t="n">
-        <v>1.11495702046316</v>
+        <v>1.115074922661524</v>
       </c>
       <c r="G59" t="n">
-        <v>1.129783373917014</v>
+        <v>1.129903126924913</v>
       </c>
       <c r="H59" t="n">
-        <v>0.01600209327752923</v>
+        <v>0.0160021622942953</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.926525873628945</v>
+        <v>-0.9266375375205114</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3846,16 +3846,16 @@
         <v>5.66083438890224</v>
       </c>
       <c r="F60" t="n">
-        <v>1.133676236566434</v>
+        <v>1.13379519218443</v>
       </c>
       <c r="G60" t="n">
-        <v>1.130094987993192</v>
+        <v>1.130214684778796</v>
       </c>
       <c r="H60" t="n">
-        <v>0.01601481588418293</v>
+        <v>0.01601487831146685</v>
       </c>
       <c r="I60" t="n">
-        <v>0.223620964433258</v>
+        <v>0.2235738128007271</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3905,16 +3905,16 @@
         <v>5.694447350642657</v>
       </c>
       <c r="F61" t="n">
-        <v>1.117478634064746</v>
+        <v>1.117598296018657</v>
       </c>
       <c r="G61" t="n">
-        <v>1.128720463885809</v>
+        <v>1.128840141324366</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01584988559482496</v>
+        <v>0.01584993097350644</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.709268830604905</v>
+        <v>-0.709267776907046</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3964,16 +3964,16 @@
         <v>5.688985012996693</v>
       </c>
       <c r="F62" t="n">
-        <v>1.130652043465206</v>
+        <v>1.130771590634669</v>
       </c>
       <c r="G62" t="n">
-        <v>1.127657766984672</v>
+        <v>1.127777427164836</v>
       </c>
       <c r="H62" t="n">
-        <v>0.01489742979091636</v>
+        <v>0.0148974582829823</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2009928237661461</v>
+        <v>0.2009848534534332</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -4023,16 +4023,16 @@
         <v>5.703151986226595</v>
       </c>
       <c r="F63" t="n">
-        <v>1.121983516373925</v>
+        <v>1.122103361245271</v>
       </c>
       <c r="G63" t="n">
-        <v>1.127410102215705</v>
+        <v>1.127529768296425</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01495112292899852</v>
+        <v>0.01495114790175834</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.3629550681611027</v>
+        <v>-0.362942503599702</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -4082,16 +4082,16 @@
         <v>5.721221686860314</v>
       </c>
       <c r="F64" t="n">
-        <v>1.111716875117168</v>
+        <v>1.111837099701513</v>
       </c>
       <c r="G64" t="n">
-        <v>1.126256113272987</v>
+        <v>1.126375776262594</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01523891811370703</v>
+        <v>0.01523889627168938</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.9540859821761901</v>
+        <v>-0.9540504969569495</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -4141,16 +4141,16 @@
         <v>5.759313628223341</v>
       </c>
       <c r="F65" t="n">
-        <v>1.106723344363796</v>
+        <v>1.106844369404419</v>
       </c>
       <c r="G65" t="n">
-        <v>1.12435430123908</v>
+        <v>1.124473998830738</v>
       </c>
       <c r="H65" t="n">
-        <v>0.01518149963773092</v>
+        <v>0.01518134706401714</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.161344880018659</v>
+        <v>-1.161269112153095</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -4200,16 +4200,16 @@
         <v>5.762993912430139</v>
       </c>
       <c r="F66" t="n">
-        <v>1.1141059190858</v>
+        <v>1.114227021463163</v>
       </c>
       <c r="G66" t="n">
-        <v>1.122670866965162</v>
+        <v>1.122790597360434</v>
       </c>
       <c r="H66" t="n">
-        <v>0.01428823661100067</v>
+        <v>0.01428796094483416</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5994405126779365</v>
+        <v>-0.5993560543967172</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -4259,16 +4259,16 @@
         <v>5.759061472992551</v>
       </c>
       <c r="F67" t="n">
-        <v>1.142243965822793</v>
+        <v>1.142364985564678</v>
       </c>
       <c r="G67" t="n">
-        <v>1.122578855574867</v>
+        <v>1.122698632318514</v>
       </c>
       <c r="H67" t="n">
-        <v>0.01414832465767295</v>
+        <v>0.01414811159993049</v>
       </c>
       <c r="I67" t="n">
-        <v>1.389925006934412</v>
+        <v>1.390033794069074</v>
       </c>
       <c r="J67" t="n">
         <v>-1</v>
@@ -4318,16 +4318,16 @@
         <v>5.771809262772875</v>
       </c>
       <c r="F68" t="n">
-        <v>1.136774965406905</v>
+        <v>1.136896253028241</v>
       </c>
       <c r="G68" t="n">
-        <v>1.122859595114694</v>
+        <v>1.122979436005757</v>
       </c>
       <c r="H68" t="n">
-        <v>0.01438134926315747</v>
+        <v>0.01438120968180669</v>
       </c>
       <c r="I68" t="n">
-        <v>0.967598382987626</v>
+        <v>0.9677083729673678</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4377,16 +4377,16 @@
         <v>5.807275066409984</v>
       </c>
       <c r="F69" t="n">
-        <v>1.14887584285261</v>
+        <v>1.148997875745103</v>
       </c>
       <c r="G69" t="n">
-        <v>1.123312062584134</v>
+        <v>1.123431993546675</v>
       </c>
       <c r="H69" t="n">
-        <v>0.01506916666662325</v>
+        <v>0.01506920665133907</v>
       </c>
       <c r="I69" t="n">
-        <v>1.696429592559829</v>
+        <v>1.696564576354485</v>
       </c>
       <c r="J69" t="n">
         <v>-1</v>
@@ -4436,16 +4436,16 @@
         <v>5.819841839592116</v>
       </c>
       <c r="F70" t="n">
-        <v>1.151875219551731</v>
+        <v>1.151997516519829</v>
       </c>
       <c r="G70" t="n">
-        <v>1.124886235963045</v>
+        <v>1.125006251929851</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01633897694062399</v>
+        <v>0.01633922916011205</v>
       </c>
       <c r="I70" t="n">
-        <v>1.65181600333756</v>
+        <v>1.651930107931327</v>
       </c>
       <c r="J70" t="n">
         <v>-1</v>
@@ -4495,16 +4495,16 @@
         <v>5.816573506443499</v>
       </c>
       <c r="F71" t="n">
-        <v>1.151581766950863</v>
+        <v>1.151703995238876</v>
       </c>
       <c r="G71" t="n">
-        <v>1.126496606250726</v>
+        <v>1.126616714760057</v>
       </c>
       <c r="H71" t="n">
-        <v>0.01732458846458469</v>
+        <v>0.01732500275663296</v>
       </c>
       <c r="I71" t="n">
-        <v>1.447951317944228</v>
+        <v>1.448039046874823</v>
       </c>
       <c r="J71" t="n">
         <v>-1</v>
@@ -4554,16 +4554,16 @@
         <v>5.833277526334015</v>
       </c>
       <c r="F72" t="n">
-        <v>1.156349392018983</v>
+        <v>1.156471971321859</v>
       </c>
       <c r="G72" t="n">
-        <v>1.128793168158216</v>
+        <v>1.128913388674814</v>
       </c>
       <c r="H72" t="n">
-        <v>0.01810768112550796</v>
+        <v>0.01810828771974418</v>
       </c>
       <c r="I72" t="n">
-        <v>1.521797499622897</v>
+        <v>1.52187678225351</v>
       </c>
       <c r="J72" t="n">
         <v>-1</v>
@@ -4613,16 +4613,16 @@
         <v>5.820731377074562</v>
       </c>
       <c r="F73" t="n">
-        <v>1.167155800802261</v>
+        <v>1.167278116462918</v>
       </c>
       <c r="G73" t="n">
-        <v>1.132581472331386</v>
+        <v>1.132701812855942</v>
       </c>
       <c r="H73" t="n">
-        <v>0.01779343858832908</v>
+        <v>0.0177942329967179</v>
       </c>
       <c r="I73" t="n">
-        <v>1.943094264733797</v>
+        <v>1.943118515608581</v>
       </c>
       <c r="J73" t="n">
         <v>-1</v>
@@ -4672,16 +4672,16 @@
         <v>5.805410967834648</v>
       </c>
       <c r="F74" t="n">
-        <v>1.167205688743451</v>
+        <v>1.167327682464157</v>
       </c>
       <c r="G74" t="n">
-        <v>1.135653272419102</v>
+        <v>1.135773713160946</v>
       </c>
       <c r="H74" t="n">
-        <v>0.01821908786853837</v>
+        <v>0.01821998408930763</v>
       </c>
       <c r="I74" t="n">
-        <v>1.731832929947911</v>
+        <v>1.731832977929323</v>
       </c>
       <c r="J74" t="n">
         <v>-1</v>
@@ -4731,16 +4731,16 @@
         <v>5.826346543406457</v>
       </c>
       <c r="F75" t="n">
-        <v>1.165337032295263</v>
+        <v>1.165459465951879</v>
       </c>
       <c r="G75" t="n">
-        <v>1.137361902750265</v>
+        <v>1.137482506923358</v>
       </c>
       <c r="H75" t="n">
-        <v>0.01934364521730167</v>
+        <v>0.019344619516754</v>
       </c>
       <c r="I75" t="n">
-        <v>1.44621808509887</v>
+        <v>1.446239818999344</v>
       </c>
       <c r="J75" t="n">
         <v>-1</v>
@@ -4790,16 +4790,16 @@
         <v>5.825078484064047</v>
       </c>
       <c r="F76" t="n">
-        <v>1.152014833917419</v>
+        <v>1.152137240927295</v>
       </c>
       <c r="G76" t="n">
-        <v>1.137480953902629</v>
+        <v>1.137601718403592</v>
       </c>
       <c r="H76" t="n">
-        <v>0.01943028129778861</v>
+        <v>0.0194313684320313</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7480015236034899</v>
+        <v>0.7480442036054273</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4849,16 +4849,16 @@
         <v>5.841206605238948</v>
       </c>
       <c r="F77" t="n">
-        <v>1.182862568276891</v>
+        <v>1.182985314199811</v>
       </c>
       <c r="G77" t="n">
-        <v>1.140023694489825</v>
+        <v>1.14014467305176</v>
       </c>
       <c r="H77" t="n">
-        <v>0.02185286351801664</v>
+        <v>0.02185399016318637</v>
       </c>
       <c r="I77" t="n">
-        <v>1.960332281018795</v>
+        <v>1.960312090751177</v>
       </c>
       <c r="J77" t="n">
         <v>-1</v>
@@ -4908,16 +4908,16 @@
         <v>5.858306968534851</v>
       </c>
       <c r="F78" t="n">
-        <v>1.209962394099189</v>
+        <v>1.210085499365652</v>
       </c>
       <c r="G78" t="n">
-        <v>1.14417665301193</v>
+        <v>1.144297888505197</v>
       </c>
       <c r="H78" t="n">
-        <v>0.026604054789146</v>
+        <v>0.02660515408000967</v>
       </c>
       <c r="I78" t="n">
-        <v>2.47277122260696</v>
+        <v>2.472739329477735</v>
       </c>
       <c r="J78" t="n">
         <v>-1</v>
@@ -4967,16 +4967,16 @@
         <v>5.85670725340159</v>
       </c>
       <c r="F79" t="n">
-        <v>1.195091755715976</v>
+        <v>1.195214827366352</v>
       </c>
       <c r="G79" t="n">
-        <v>1.148183389774571</v>
+        <v>1.148304883740439</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02797105727884313</v>
+        <v>0.02797205651019888</v>
       </c>
       <c r="I79" t="n">
-        <v>1.677032279251234</v>
+        <v>1.677028773655226</v>
       </c>
       <c r="J79" t="n">
         <v>-1</v>
@@ -5026,16 +5026,16 @@
         <v>5.857164600990844</v>
       </c>
       <c r="F80" t="n">
-        <v>1.176206191718337</v>
+        <v>1.176329272979323</v>
       </c>
       <c r="G80" t="n">
-        <v>1.150309887532166</v>
+        <v>1.150431587780183</v>
       </c>
       <c r="H80" t="n">
-        <v>0.02842311970445721</v>
+        <v>0.02842410097128862</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9110999937881666</v>
+        <v>0.9111171264589403</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -5085,16 +5085,16 @@
         <v>5.952126560232704</v>
       </c>
       <c r="F81" t="n">
-        <v>1.061295779403068</v>
+        <v>1.061420856175275</v>
       </c>
       <c r="G81" t="n">
-        <v>1.147500744799082</v>
+        <v>1.147622715788014</v>
       </c>
       <c r="H81" t="n">
-        <v>0.03405676030334023</v>
+        <v>0.03405703487114223</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.531214496863318</v>
+        <v>-2.53110289662303</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -5144,16 +5144,16 @@
         <v>5.954436849899731</v>
       </c>
       <c r="F82" t="n">
-        <v>1.054024604611568</v>
+        <v>1.05414972993173</v>
       </c>
       <c r="G82" t="n">
-        <v>1.1436693728564</v>
+        <v>1.143791622752867</v>
       </c>
       <c r="H82" t="n">
-        <v>0.03986669719088096</v>
+        <v>0.03986651678390481</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.248612866413649</v>
+        <v>-2.24855091572304</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -5203,16 +5203,16 @@
         <v>5.948090365497994</v>
       </c>
       <c r="F83" t="n">
-        <v>1.058689912217301</v>
+        <v>1.058814904173736</v>
       </c>
       <c r="G83" t="n">
-        <v>1.140504692648569</v>
+        <v>1.14062719989929</v>
       </c>
       <c r="H83" t="n">
-        <v>0.04397884999816178</v>
+        <v>0.04397836467034311</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.860321050566064</v>
+        <v>-1.860285081967242</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -5262,16 +5262,16 @@
         <v>5.961515828160556</v>
       </c>
       <c r="F84" t="n">
-        <v>1.039114586461601</v>
+        <v>1.039239860537966</v>
       </c>
       <c r="G84" t="n">
-        <v>1.13687457821579</v>
+        <v>1.136997337941113</v>
       </c>
       <c r="H84" t="n">
-        <v>0.04917011623169936</v>
+        <v>0.04916933114470609</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.988199321993156</v>
+        <v>-1.988179931011161</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -5321,16 +5321,16 @@
         <v>5.98595539627007</v>
       </c>
       <c r="F85" t="n">
-        <v>1.077788945347342</v>
+        <v>1.077914732991801</v>
       </c>
       <c r="G85" t="n">
-        <v>1.135427858264968</v>
+        <v>1.135550856120482</v>
       </c>
       <c r="H85" t="n">
-        <v>0.0505113126520777</v>
+        <v>0.05051031467459768</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.141108989082174</v>
+        <v>-1.141076302929208</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -5380,16 +5380,16 @@
         <v>5.985829728516112</v>
       </c>
       <c r="F86" t="n">
-        <v>1.095382883438691</v>
+        <v>1.095508668442394</v>
       </c>
       <c r="G86" t="n">
-        <v>1.134491706482612</v>
+        <v>1.134614938469444</v>
       </c>
       <c r="H86" t="n">
-        <v>0.05109738314762458</v>
+        <v>0.05109624453940078</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7653781981541506</v>
+        <v>-0.7653452886717393</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5439,16 +5439,16 @@
         <v>5.992865390419841</v>
       </c>
       <c r="F87" t="n">
-        <v>1.1077213039358</v>
+        <v>1.107847236785466</v>
       </c>
       <c r="G87" t="n">
-        <v>1.132765573388262</v>
+        <v>1.132889051030483</v>
       </c>
       <c r="H87" t="n">
-        <v>0.05140390879291727</v>
+        <v>0.05140272918670828</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.4872055460481514</v>
+        <v>-0.487168962450576</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -5498,16 +5498,16 @@
         <v>5.962056385069926</v>
       </c>
       <c r="F88" t="n">
-        <v>1.149146533404532</v>
+        <v>1.149271818840051</v>
       </c>
       <c r="G88" t="n">
-        <v>1.133384151788144</v>
+        <v>1.133507829321074</v>
       </c>
       <c r="H88" t="n">
-        <v>0.05152898151657757</v>
+        <v>0.05152784146295274</v>
       </c>
       <c r="I88" t="n">
-        <v>0.305893521518902</v>
+        <v>0.3059314939538245</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -5557,16 +5557,16 @@
         <v>5.958731556573001</v>
       </c>
       <c r="F89" t="n">
-        <v>1.15759934330762</v>
+        <v>1.157724558875872</v>
       </c>
       <c r="G89" t="n">
-        <v>1.133820326810894</v>
+        <v>1.133944163477612</v>
       </c>
       <c r="H89" t="n">
-        <v>0.05170363970790831</v>
+        <v>0.05170256594109949</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4599099141000788</v>
+        <v>0.4599461354655137</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5616,16 +5616,16 @@
         <v>5.997396093626087</v>
       </c>
       <c r="F90" t="n">
-        <v>1.152713344230624</v>
+        <v>1.152839372287562</v>
       </c>
       <c r="G90" t="n">
-        <v>1.133862233044839</v>
+        <v>1.133986256265999</v>
       </c>
       <c r="H90" t="n">
-        <v>0.05171938079907197</v>
+        <v>0.0517183776238547</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3644883386949449</v>
+        <v>0.3645341731073014</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -5675,16 +5675,16 @@
         <v>5.993538886487244</v>
       </c>
       <c r="F91" t="n">
-        <v>1.198403965306636</v>
+        <v>1.198529912309011</v>
       </c>
       <c r="G91" t="n">
-        <v>1.136203342962627</v>
+        <v>1.136327552119506</v>
       </c>
       <c r="H91" t="n">
-        <v>0.05358958562568128</v>
+        <v>0.05358876209393353</v>
       </c>
       <c r="I91" t="n">
-        <v>1.160684890875531</v>
+        <v>1.160735157130024</v>
       </c>
       <c r="J91" t="n">
         <v>-1</v>
@@ -5734,16 +5734,16 @@
         <v>5.982784867071093</v>
       </c>
       <c r="F92" t="n">
-        <v>1.160845344567659</v>
+        <v>1.160971065587266</v>
       </c>
       <c r="G92" t="n">
-        <v>1.136428140590061</v>
+        <v>1.136552506832776</v>
       </c>
       <c r="H92" t="n">
-        <v>0.05368788177202295</v>
+        <v>0.05368712776772819</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4547991682980042</v>
+        <v>0.4548307903550858</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5793,16 +5793,16 @@
         <v>5.983188051122531</v>
       </c>
       <c r="F93" t="n">
-        <v>1.14715474314571</v>
+        <v>1.147280472637744</v>
       </c>
       <c r="G93" t="n">
-        <v>1.135428087707234</v>
+        <v>1.135552624641517</v>
       </c>
       <c r="H93" t="n">
-        <v>0.05327004348207891</v>
+        <v>0.05326936363834962</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2201360215225118</v>
+        <v>0.2201612182914076</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5852,16 +5852,16 @@
         <v>5.959531545016149</v>
       </c>
       <c r="F94" t="n">
-        <v>1.156260033838677</v>
+        <v>1.156385266217722</v>
       </c>
       <c r="G94" t="n">
-        <v>1.134880804961995</v>
+        <v>1.135005503829196</v>
       </c>
       <c r="H94" t="n">
-        <v>0.05298183243886066</v>
+        <v>0.05298124533018352</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4035199971868288</v>
+        <v>0.4035345385954198</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5911,16 +5911,16 @@
         <v>5.962750867995942</v>
       </c>
       <c r="F95" t="n">
-        <v>1.166850909122108</v>
+        <v>1.16697620915135</v>
       </c>
       <c r="G95" t="n">
-        <v>1.134956498803337</v>
+        <v>1.135081340989169</v>
       </c>
       <c r="H95" t="n">
-        <v>0.0530286953046184</v>
+        <v>0.05302819604618215</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6014556861253436</v>
+        <v>0.6014699827692328</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5970,16 +5970,16 @@
         <v>5.959531545016149</v>
       </c>
       <c r="F96" t="n">
-        <v>1.151261364278356</v>
+        <v>1.1513865966574</v>
       </c>
       <c r="G96" t="n">
-        <v>1.134918825321384</v>
+        <v>1.135043808775674</v>
       </c>
       <c r="H96" t="n">
-        <v>0.05301620479376808</v>
+        <v>0.05301575307530886</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3082555422543675</v>
+        <v>0.3082628640304559</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -6029,16 +6029,16 @@
         <v>5.94735954974672</v>
       </c>
       <c r="F97" t="n">
-        <v>1.140693202264512</v>
+        <v>1.140818178863733</v>
       </c>
       <c r="G97" t="n">
-        <v>1.132810357020765</v>
+        <v>1.13293545200887</v>
       </c>
       <c r="H97" t="n">
-        <v>0.0518344884237897</v>
+        <v>0.05183414006595252</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1520772266390961</v>
+        <v>0.1520759646988046</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -6088,16 +6088,16 @@
         <v>5.962673683416126</v>
       </c>
       <c r="F98" t="n">
-        <v>1.127615292588263</v>
+        <v>1.127740590995563</v>
       </c>
       <c r="G98" t="n">
-        <v>1.128693001945219</v>
+        <v>1.128818206590366</v>
       </c>
       <c r="H98" t="n">
-        <v>0.04855001177608873</v>
+        <v>0.04854981491006437</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.02219792163854965</v>
+        <v>-0.02219608039287325</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -6147,16 +6147,16 @@
         <v>5.962545055387006</v>
       </c>
       <c r="F99" t="n">
-        <v>1.117132593241973</v>
+        <v>1.117257888946309</v>
       </c>
       <c r="G99" t="n">
-        <v>1.124795043821519</v>
+        <v>1.124920359669364</v>
       </c>
       <c r="H99" t="n">
-        <v>0.04600110766521245</v>
+        <v>0.04600107064509103</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.1665710016226581</v>
+        <v>-0.166571573565588</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -6206,16 +6206,16 @@
         <v>5.965882922901972</v>
       </c>
       <c r="F100" t="n">
-        <v>1.12248944685128</v>
+        <v>1.122614812696884</v>
       </c>
       <c r="G100" t="n">
-        <v>1.122109206578166</v>
+        <v>1.122234636655242</v>
       </c>
       <c r="H100" t="n">
-        <v>0.04438104825347484</v>
+        <v>0.04438115325839519</v>
       </c>
       <c r="I100" t="n">
-        <v>0.008567627130901973</v>
+        <v>0.008566159590953464</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -6265,16 +6265,16 @@
         <v>5.940468433706842</v>
       </c>
       <c r="F101" t="n">
-        <v>1.125944501473731</v>
+        <v>1.126069333264446</v>
       </c>
       <c r="G101" t="n">
-        <v>1.125341642681699</v>
+        <v>1.1254670605097</v>
       </c>
       <c r="H101" t="n">
-        <v>0.04200960738259412</v>
+        <v>0.04200968951430623</v>
       </c>
       <c r="I101" t="n">
-        <v>0.01435049812632295</v>
+        <v>0.01433652001976859</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -6324,16 +6324,16 @@
         <v>5.929975570597685</v>
       </c>
       <c r="F102" t="n">
-        <v>1.194138458809176</v>
+        <v>1.19426307010501</v>
       </c>
       <c r="G102" t="n">
-        <v>1.132347335391579</v>
+        <v>1.132472727518364</v>
       </c>
       <c r="H102" t="n">
-        <v>0.04116502253103407</v>
+        <v>0.04116501333812039</v>
       </c>
       <c r="I102" t="n">
-        <v>1.501058899482267</v>
+        <v>1.501040266381391</v>
       </c>
       <c r="J102" t="n">
         <v>-1</v>
@@ -6383,16 +6383,16 @@
         <v>5.890632658072621</v>
       </c>
       <c r="F103" t="n">
-        <v>1.215235149844114</v>
+        <v>1.215358934396017</v>
       </c>
       <c r="G103" t="n">
-        <v>1.14017459727292</v>
+        <v>1.140299929029478</v>
       </c>
       <c r="H103" t="n">
-        <v>0.04130520277187692</v>
+        <v>0.04130499830860931</v>
       </c>
       <c r="I103" t="n">
-        <v>1.817217869277702</v>
+        <v>1.817189406612167</v>
       </c>
       <c r="J103" t="n">
         <v>-1</v>
@@ -6442,16 +6442,16 @@
         <v>5.882697390434339</v>
       </c>
       <c r="F104" t="n">
-        <v>1.183989726946954</v>
+        <v>1.184113344748763</v>
       </c>
       <c r="G104" t="n">
-        <v>1.147418354297188</v>
+        <v>1.147543603240018</v>
       </c>
       <c r="H104" t="n">
-        <v>0.03484814820355922</v>
+        <v>0.03484780175225395</v>
       </c>
       <c r="I104" t="n">
-        <v>1.04944952702051</v>
+        <v>1.04941315290797</v>
       </c>
       <c r="J104" t="n">
         <v>-1</v>
@@ -6501,16 +6501,16 @@
         <v>5.918807384063352</v>
       </c>
       <c r="F105" t="n">
-        <v>1.177513240618361</v>
+        <v>1.177637617228203</v>
       </c>
       <c r="G105" t="n">
-        <v>1.152404569060739</v>
+        <v>1.152529747451838</v>
       </c>
       <c r="H105" t="n">
-        <v>0.03131644604906979</v>
+        <v>0.03131609126999332</v>
       </c>
       <c r="I105" t="n">
-        <v>0.8017727017388721</v>
+        <v>0.8017561821459879</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -6560,16 +6560,16 @@
         <v>5.908924968232186</v>
       </c>
       <c r="F106" t="n">
-        <v>1.12052219744635</v>
+        <v>1.120646366389124</v>
       </c>
       <c r="G106" t="n">
-        <v>1.153661534761122</v>
+        <v>1.153786632349175</v>
       </c>
       <c r="H106" t="n">
-        <v>0.0293500558619402</v>
+        <v>0.02934980069856702</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.129106447723837</v>
+        <v>-1.129147904628485</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -6619,16 +6619,16 @@
         <v>5.895256457589491</v>
       </c>
       <c r="F107" t="n">
-        <v>1.147357090962278</v>
+        <v>1.14748097267776</v>
       </c>
       <c r="G107" t="n">
-        <v>1.155643324112446</v>
+        <v>1.155768319143789</v>
       </c>
       <c r="H107" t="n">
-        <v>0.02735515079521461</v>
+        <v>0.02735497342249278</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.3029130861752357</v>
+        <v>-0.3029557491441568</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -6678,16 +6678,16 @@
         <v>5.897867925179888</v>
       </c>
       <c r="F108" t="n">
-        <v>1.143340433196783</v>
+        <v>1.143464369789111</v>
       </c>
       <c r="G108" t="n">
-        <v>1.155353019102058</v>
+        <v>1.155477946691243</v>
       </c>
       <c r="H108" t="n">
-        <v>0.02745834023518157</v>
+        <v>0.02745819135595296</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.4374840504701717</v>
+        <v>-0.4375225136424325</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -6737,16 +6737,16 @@
         <v>5.875997591000409</v>
       </c>
       <c r="F109" t="n">
-        <v>1.120860662844942</v>
+        <v>1.120984139858534</v>
       </c>
       <c r="G109" t="n">
-        <v>1.153516085078924</v>
+        <v>1.153640925740376</v>
       </c>
       <c r="H109" t="n">
-        <v>0.02850894472430238</v>
+        <v>0.02850888661294745</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.145444791092014</v>
+        <v>-1.145494958298751</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -6796,16 +6796,16 @@
         <v>5.879890291127706</v>
       </c>
       <c r="F110" t="n">
-        <v>1.140052265775034</v>
+        <v>1.140175824589031</v>
       </c>
       <c r="G110" t="n">
-        <v>1.152883031156145</v>
+        <v>1.153007748355449</v>
       </c>
       <c r="H110" t="n">
-        <v>0.02866783779096138</v>
+        <v>0.02866781056695225</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4475665543620606</v>
+        <v>-0.4476073865651421</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -6855,16 +6855,16 @@
         <v>5.885214726902118</v>
       </c>
       <c r="F111" t="n">
-        <v>1.137825816460904</v>
+        <v>1.137949487161507</v>
       </c>
       <c r="G111" t="n">
-        <v>1.149854123713858</v>
+        <v>1.149978727098074</v>
       </c>
       <c r="H111" t="n">
-        <v>0.026740598161966</v>
+        <v>0.02674047623377018</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4498144424481425</v>
+        <v>-0.4498513725561356</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -6914,16 +6914,16 @@
         <v>5.911744720499765</v>
       </c>
       <c r="F112" t="n">
-        <v>1.153725485457355</v>
+        <v>1.153849713653827</v>
       </c>
       <c r="G112" t="n">
-        <v>1.149498130758343</v>
+        <v>1.149622659501402</v>
       </c>
       <c r="H112" t="n">
-        <v>0.02663375193181083</v>
+        <v>0.02663360131760112</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1587217118277306</v>
+        <v>0.1587113249169001</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -6973,16 +6973,16 @@
         <v>5.9222484364193</v>
       </c>
       <c r="F113" t="n">
-        <v>1.122245144563881</v>
+        <v>1.122369593483295</v>
       </c>
       <c r="G113" t="n">
-        <v>1.148252650829252</v>
+        <v>1.148377115543679</v>
       </c>
       <c r="H113" t="n">
-        <v>0.02732262170829436</v>
+        <v>0.02732248142851952</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.9518671576628125</v>
+        <v>-0.9518726228590999</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -7020,28 +7020,28 @@
         <v>46190</v>
       </c>
       <c r="B114" t="n">
-        <v>205.3699951171875</v>
+        <v>205</v>
       </c>
       <c r="C114" t="n">
-        <v>363.614990234375</v>
+        <v>362.8299865722656</v>
       </c>
       <c r="D114" t="n">
-        <v>5.324813206576316</v>
+        <v>5.323009979138408</v>
       </c>
       <c r="E114" t="n">
-        <v>5.896095588720761</v>
+        <v>5.893934368001432</v>
       </c>
       <c r="F114" t="n">
-        <v>1.130963153834694</v>
+        <v>1.130821040961587</v>
       </c>
       <c r="G114" t="n">
-        <v>1.146987806829052</v>
+        <v>1.147098904280873</v>
       </c>
       <c r="H114" t="n">
-        <v>0.02751726673242495</v>
+        <v>0.02752534777608156</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5823490083582963</v>
+        <v>-0.5913772080812839</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -7056,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>-0.009835632365376323</v>
+        <v>-0.01161951506464221</v>
       </c>
       <c r="O114" t="n">
-        <v>-0.02581382388647024</v>
+        <v>-0.02791698172199431</v>
       </c>
       <c r="P114" t="n">
         <v>-0</v>

--- a/trades_taken.xlsx
+++ b/trades_taken.xlsx
@@ -548,7 +548,7 @@
         <v>5.749174382292647</v>
       </c>
       <c r="F2" t="n">
-        <v>1.141947091075164</v>
+        <v>1.144989835990965</v>
       </c>
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr"/>
@@ -582,16 +582,16 @@
         <v>188.8796234130859</v>
       </c>
       <c r="C3" t="n">
-        <v>321.5614624023438</v>
+        <v>321.5614318847656</v>
       </c>
       <c r="D3" t="n">
         <v>5.241109898986017</v>
       </c>
       <c r="E3" t="n">
-        <v>5.773188699286039</v>
+        <v>5.773188604381696</v>
       </c>
       <c r="F3" t="n">
-        <v>1.134803942382518</v>
+        <v>1.137859464304636</v>
       </c>
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr"/>
@@ -612,7 +612,7 @@
         <v>0.009987097761727348</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02430498275331261</v>
+        <v>0.02430488554232513</v>
       </c>
       <c r="P3" t="n">
         <v>0</v>
@@ -644,7 +644,7 @@
         <v>5.78387729560523</v>
       </c>
       <c r="F4" t="n">
-        <v>1.105444573123957</v>
+        <v>1.10850568452267</v>
       </c>
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr"/>
@@ -665,7 +665,7 @@
         <v>-0.02152189920922831</v>
       </c>
       <c r="O4" t="n">
-        <v>0.01074592343155878</v>
+        <v>0.01074601935574182</v>
       </c>
       <c r="P4" t="n">
         <v>-0</v>
@@ -697,7 +697,7 @@
         <v>5.793449133348831</v>
       </c>
       <c r="F5" t="n">
-        <v>1.097663168379113</v>
+        <v>1.100729345663584</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -741,16 +741,16 @@
         <v>184.7147064208984</v>
       </c>
       <c r="C6" t="n">
-        <v>331.4285888671875</v>
+        <v>331.4285583496094</v>
       </c>
       <c r="D6" t="n">
         <v>5.21881250732129</v>
       </c>
       <c r="E6" t="n">
-        <v>5.803412368221555</v>
+        <v>5.803412276142656</v>
       </c>
       <c r="F6" t="n">
-        <v>1.091009309202772</v>
+        <v>1.094080824963935</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -771,7 +771,7 @@
         <v>0.0004328018336186013</v>
       </c>
       <c r="O6" t="n">
-        <v>0.01001303314384083</v>
+        <v>0.01001294014295717</v>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -794,16 +794,16 @@
         <v>185.5836486816406</v>
       </c>
       <c r="C7" t="n">
-        <v>335.5332336425781</v>
+        <v>335.5332641601562</v>
       </c>
       <c r="D7" t="n">
         <v>5.223505716695444</v>
       </c>
       <c r="E7" t="n">
-        <v>5.815721008562775</v>
+        <v>5.815721099515246</v>
       </c>
       <c r="F7" t="n">
-        <v>1.08694773057613</v>
+        <v>1.090025630584978</v>
       </c>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
@@ -824,7 +824,7 @@
         <v>0.004704239730442428</v>
       </c>
       <c r="O7" t="n">
-        <v>0.01238470341203879</v>
+        <v>0.01238488871021493</v>
       </c>
       <c r="P7" t="n">
         <v>0</v>
@@ -856,7 +856,7 @@
         <v>5.815334021863411</v>
       </c>
       <c r="F8" t="n">
-        <v>1.072749221399825</v>
+        <v>1.075826981240126</v>
       </c>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
@@ -877,7 +877,7 @@
         <v>-0.01436952051443752</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0003869118296699892</v>
+        <v>-0.0003870027469463633</v>
       </c>
       <c r="P8" t="n">
         <v>-0</v>
@@ -900,16 +900,16 @@
         <v>186.8221282958984</v>
       </c>
       <c r="C9" t="n">
-        <v>332.347412109375</v>
+        <v>332.3473815917969</v>
       </c>
       <c r="D9" t="n">
         <v>5.230156978607081</v>
       </c>
       <c r="E9" t="n">
-        <v>5.806180843814804</v>
+        <v>5.806180751990471</v>
       </c>
       <c r="F9" t="n">
-        <v>1.100384642043344</v>
+        <v>1.103457622836575</v>
       </c>
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr"/>
@@ -930,7 +930,7 @@
         <v>0.02134973667048112</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.009111415232374798</v>
+        <v>-0.0091115062200543</v>
       </c>
       <c r="P9" t="n">
         <v>0</v>
@@ -962,7 +962,7 @@
         <v>5.797791852433679</v>
       </c>
       <c r="F10" t="n">
-        <v>1.101958006965488</v>
+        <v>1.105026482629785</v>
       </c>
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr"/>
@@ -983,7 +983,7 @@
         <v>-0.004383850305160086</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.008353901983038203</v>
+        <v>-0.008353810925792238</v>
       </c>
       <c r="P10" t="n">
         <v>-0</v>
@@ -1015,7 +1015,7 @@
         <v>5.773250764797821</v>
       </c>
       <c r="F11" t="n">
-        <v>1.07460776127258</v>
+        <v>1.077663248590261</v>
       </c>
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr"/>
@@ -1068,7 +1068,7 @@
         <v>5.792870686585944</v>
       </c>
       <c r="F12" t="n">
-        <v>1.089709203072231</v>
+        <v>1.092775074214319</v>
       </c>
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr"/>
@@ -1112,16 +1112,16 @@
         <v>184.6148223876953</v>
       </c>
       <c r="C13" t="n">
-        <v>330.1102905273438</v>
+        <v>330.1103210449219</v>
       </c>
       <c r="D13" t="n">
         <v>5.218271613469879</v>
       </c>
       <c r="E13" t="n">
-        <v>5.799426812342785</v>
+        <v>5.799426904789393</v>
       </c>
       <c r="F13" t="n">
-        <v>1.093303228605845</v>
+        <v>1.096372503865342</v>
       </c>
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr"/>
@@ -1142,7 +1142,7 @@
         <v>0.008291397296120495</v>
       </c>
       <c r="O13" t="n">
-        <v>0.006577664193148758</v>
+        <v>0.00657775724784404</v>
       </c>
       <c r="P13" t="n">
         <v>0</v>
@@ -1174,7 +1174,7 @@
         <v>5.791499330208546</v>
       </c>
       <c r="F14" t="n">
-        <v>1.114136342887822</v>
+        <v>1.117201488240889</v>
       </c>
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr"/>
@@ -1195,7 +1195,7 @@
         <v>0.01531054391066577</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.007896142517177074</v>
+        <v>-0.007896234233809474</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -1227,7 +1227,7 @@
         <v>5.807622181149471</v>
       </c>
       <c r="F15" t="n">
-        <v>1.09625391397329</v>
+        <v>1.099327592329439</v>
       </c>
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr"/>
@@ -1280,7 +1280,7 @@
         <v>5.811485489879658</v>
       </c>
       <c r="F16" t="n">
-        <v>1.104439774354512</v>
+        <v>1.107515497363027</v>
       </c>
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr"/>
@@ -1324,16 +1324,16 @@
         <v>191.2866821289062</v>
       </c>
       <c r="C17" t="n">
-        <v>335.5731811523438</v>
+        <v>335.5732116699219</v>
       </c>
       <c r="D17" t="n">
         <v>5.253773256296206</v>
       </c>
       <c r="E17" t="n">
-        <v>5.815840058266167</v>
+        <v>5.81584014920781</v>
       </c>
       <c r="F17" t="n">
-        <v>1.117130593487522</v>
+        <v>1.120208556511004</v>
       </c>
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr"/>
@@ -1354,7 +1354,7 @@
         <v>0.01591339111278667</v>
       </c>
       <c r="O17" t="n">
-        <v>0.00436406329650052</v>
+        <v>0.004364154635023487</v>
       </c>
       <c r="P17" t="n">
         <v>0</v>
@@ -1377,16 +1377,16 @@
         <v>192.2754821777344</v>
       </c>
       <c r="C18" t="n">
-        <v>337.810302734375</v>
+        <v>337.8102722167969</v>
       </c>
       <c r="D18" t="n">
         <v>5.25892914669051</v>
       </c>
       <c r="E18" t="n">
-        <v>5.822484503418294</v>
+        <v>5.822484413078896</v>
       </c>
       <c r="F18" t="n">
-        <v>1.11756047783427</v>
+        <v>1.120642086267985</v>
       </c>
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr"/>
@@ -1407,7 +1407,7 @@
         <v>0.005169204870006494</v>
       </c>
       <c r="O18" t="n">
-        <v>0.006666568449686716</v>
+        <v>0.006666385960138577</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
@@ -1439,7 +1439,7 @@
         <v>5.821745073183263</v>
       </c>
       <c r="F19" t="n">
-        <v>1.110892178423948</v>
+        <v>1.113973331306886</v>
       </c>
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr"/>
@@ -1460,7 +1460,7 @@
         <v>-0.007168418675203125</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.0007391569238641704</v>
+        <v>-0.0007390666512366861</v>
       </c>
       <c r="P19" t="n">
         <v>-0</v>
@@ -1483,16 +1483,16 @@
         <v>185.3838806152344</v>
       </c>
       <c r="C20" t="n">
-        <v>343.2431945800781</v>
+        <v>343.2432250976562</v>
       </c>
       <c r="D20" t="n">
         <v>5.222428705529022</v>
       </c>
       <c r="E20" t="n">
-        <v>5.838439218027872</v>
+        <v>5.838439306937361</v>
       </c>
       <c r="F20" t="n">
-        <v>1.069711899092362</v>
+        <v>1.072801824143372</v>
       </c>
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr"/>
@@ -1513,7 +1513,7 @@
         <v>-0.02888094347234282</v>
       </c>
       <c r="O20" t="n">
-        <v>0.01683427075541455</v>
+        <v>0.01683436116163306</v>
       </c>
       <c r="P20" t="n">
         <v>-0</v>
@@ -1545,16 +1545,16 @@
         <v>5.826791450769824</v>
       </c>
       <c r="F21" t="n">
-        <v>1.049192883832851</v>
+        <v>1.052276707506189</v>
       </c>
       <c r="G21" t="n">
-        <v>1.098492297099277</v>
+        <v>1.101562989153798</v>
       </c>
       <c r="H21" t="n">
-        <v>0.02201266124285643</v>
+        <v>0.02200673120783475</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.239593510413244</v>
+        <v>-2.239600292389763</v>
       </c>
       <c r="J21" t="n">
         <v>1</v>
@@ -1572,7 +1572,7 @@
         <v>-0.0283928694598331</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.01158019462821291</v>
+        <v>-0.01158028250810805</v>
       </c>
       <c r="P21" t="n">
         <v>-0</v>
@@ -1595,25 +1595,25 @@
         <v>173.9778137207031</v>
       </c>
       <c r="C22" t="n">
-        <v>332.6070861816406</v>
+        <v>332.6070556640625</v>
       </c>
       <c r="D22" t="n">
         <v>5.158927783732494</v>
       </c>
       <c r="E22" t="n">
-        <v>5.806961871948709</v>
+        <v>5.806961780196065</v>
       </c>
       <c r="F22" t="n">
-        <v>1.02859992393098</v>
+        <v>1.031673318031634</v>
       </c>
       <c r="G22" t="n">
-        <v>1.092824938742068</v>
+        <v>1.095897163255832</v>
       </c>
       <c r="H22" t="n">
-        <v>0.02466708176955401</v>
+        <v>0.02466434843618363</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.603673000766515</v>
+        <v>-2.6039141228632</v>
       </c>
       <c r="J22" t="n">
         <v>1</v>
@@ -1631,19 +1631,19 @@
         <v>-0.03410213375324578</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.01963426584484906</v>
+        <v>-0.01963435579599293</v>
       </c>
       <c r="P22" t="n">
         <v>-0.03437991153102356</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.01991204362262684</v>
+        <v>0.01991213357377071</v>
       </c>
       <c r="R22" t="n">
-        <v>-0.01446786790839672</v>
+        <v>-0.01446777795725285</v>
       </c>
       <c r="S22" t="n">
-        <v>98.55321320916033</v>
+        <v>98.55322220427472</v>
       </c>
     </row>
     <row r="23">
@@ -1654,25 +1654,25 @@
         <v>171.6706237792969</v>
       </c>
       <c r="C23" t="n">
-        <v>330.8193969726562</v>
+        <v>330.8193664550781</v>
       </c>
       <c r="D23" t="n">
         <v>5.145577662871488</v>
       </c>
       <c r="E23" t="n">
-        <v>5.801572597986273</v>
+        <v>5.801572505737814</v>
       </c>
       <c r="F23" t="n">
-        <v>1.019083041324676</v>
+        <v>1.022153583509755</v>
       </c>
       <c r="G23" t="n">
-        <v>1.087038893689176</v>
+        <v>1.090111869216088</v>
       </c>
       <c r="H23" t="n">
-        <v>0.0276889659559465</v>
+        <v>0.02768826456116998</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.454257499995431</v>
+        <v>-2.454407554370058</v>
       </c>
       <c r="J23" t="n">
         <v>1</v>
@@ -1690,19 +1690,19 @@
         <v>-0.01326140323334624</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.005374777878328518</v>
+        <v>-0.005374778371478595</v>
       </c>
       <c r="P23" t="n">
         <v>-0.01334076831271132</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.005374777878328518</v>
+        <v>0.005374778371478595</v>
       </c>
       <c r="R23" t="n">
-        <v>-0.007965990434382798</v>
+        <v>-0.007965989941232722</v>
       </c>
       <c r="S23" t="n">
-        <v>97.76813925545846</v>
+        <v>97.76814822751938</v>
       </c>
     </row>
     <row r="24">
@@ -1722,16 +1722,16 @@
         <v>5.775917931798511</v>
       </c>
       <c r="F24" t="n">
-        <v>1.113103515400194</v>
+        <v>1.1161604143134</v>
       </c>
       <c r="G24" t="n">
-        <v>1.087421840802988</v>
+        <v>1.090494605705624</v>
       </c>
       <c r="H24" t="n">
-        <v>0.02800804431260939</v>
+        <v>0.02800697695924986</v>
       </c>
       <c r="I24" t="n">
-        <v>0.9169392304068992</v>
+        <v>0.9164076738849621</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
@@ -1749,19 +1749,19 @@
         <v>0.07871771529462501</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.02532838143629002</v>
+        <v>-0.02532829152433114</v>
       </c>
       <c r="P24" t="n">
         <v>0.07863835021525993</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.02532838143629002</v>
+        <v>0.02532829152433114</v>
       </c>
       <c r="R24" t="n">
-        <v>0.1039667316515499</v>
+        <v>0.1039666417395911</v>
       </c>
       <c r="S24" t="n">
-        <v>107.9327731535021</v>
+        <v>107.9327742678331</v>
       </c>
     </row>
     <row r="25">
@@ -1781,16 +1781,16 @@
         <v>5.780429907926294</v>
       </c>
       <c r="F25" t="n">
-        <v>1.13455917668789</v>
+        <v>1.137618463560046</v>
       </c>
       <c r="G25" t="n">
-        <v>1.089266641218427</v>
+        <v>1.092339061600448</v>
       </c>
       <c r="H25" t="n">
-        <v>0.02987124849863178</v>
+        <v>0.02986926966460488</v>
       </c>
       <c r="I25" t="n">
-        <v>1.516258534407675</v>
+        <v>1.515919286545352</v>
       </c>
       <c r="J25" t="n">
         <v>-1</v>
@@ -1820,7 +1820,7 @@
         <v>-7.936507936507937e-05</v>
       </c>
       <c r="S25" t="n">
-        <v>107.9242070603947</v>
+        <v>107.9242081746373</v>
       </c>
     </row>
     <row r="26">
@@ -1840,16 +1840,16 @@
         <v>5.762572732764129</v>
       </c>
       <c r="F26" t="n">
-        <v>1.139336110013565</v>
+        <v>1.142385945993242</v>
       </c>
       <c r="G26" t="n">
-        <v>1.091682981258966</v>
+        <v>1.094754317651913</v>
       </c>
       <c r="H26" t="n">
-        <v>0.03190502276937025</v>
+        <v>0.03190139396192865</v>
       </c>
       <c r="I26" t="n">
-        <v>1.493593315982446</v>
+        <v>1.493089248644529</v>
       </c>
       <c r="J26" t="n">
         <v>-1</v>
@@ -1879,7 +1879,7 @@
         <v>-0.009805625009529749</v>
       </c>
       <c r="S26" t="n">
-        <v>106.8659427565096</v>
+        <v>106.8659438598263</v>
       </c>
     </row>
     <row r="27">
@@ -1890,25 +1890,25 @@
         <v>189.8184967041016</v>
       </c>
       <c r="C27" t="n">
-        <v>310.5557250976562</v>
+        <v>310.5557556152344</v>
       </c>
       <c r="D27" t="n">
         <v>5.246068335084544</v>
       </c>
       <c r="E27" t="n">
-        <v>5.738363354184461</v>
+        <v>5.738363452452096</v>
       </c>
       <c r="F27" t="n">
-        <v>1.164532662197749</v>
+        <v>1.167569615544519</v>
       </c>
       <c r="G27" t="n">
-        <v>1.095562227840047</v>
+        <v>1.09863151689989</v>
       </c>
       <c r="H27" t="n">
-        <v>0.03578029552809846</v>
+        <v>0.03577365499565219</v>
       </c>
       <c r="I27" t="n">
-        <v>1.927609410144153</v>
+        <v>1.927063327831824</v>
       </c>
       <c r="J27" t="n">
         <v>-1</v>
@@ -1926,19 +1926,19 @@
         <v>0.008009007297158588</v>
       </c>
       <c r="O27" t="n">
-        <v>-0.0239186821589582</v>
+        <v>-0.02391858624175092</v>
       </c>
       <c r="P27" t="n">
         <v>-0.007929642217793508</v>
       </c>
       <c r="Q27" t="n">
-        <v>-0.0239186821589582</v>
+        <v>-0.02391858624175092</v>
       </c>
       <c r="R27" t="n">
-        <v>-0.03184832437675171</v>
+        <v>-0.03184822845954442</v>
       </c>
       <c r="S27" t="n">
-        <v>103.4624415467729</v>
+        <v>103.4624528652338</v>
       </c>
     </row>
     <row r="28">
@@ -1949,25 +1949,25 @@
         <v>186.7122802734375</v>
       </c>
       <c r="C28" t="n">
-        <v>308.5983276367188</v>
+        <v>308.5982971191406</v>
       </c>
       <c r="D28" t="n">
         <v>5.229568823818084</v>
       </c>
       <c r="E28" t="n">
-        <v>5.732040520720335</v>
+        <v>5.732040421829392</v>
       </c>
       <c r="F28" t="n">
-        <v>1.152530403674744</v>
+        <v>1.155564150797069</v>
       </c>
       <c r="G28" t="n">
-        <v>1.099551286953793</v>
+        <v>1.102618375377737</v>
       </c>
       <c r="H28" t="n">
-        <v>0.03750863013418261</v>
+        <v>0.03749997234285033</v>
       </c>
       <c r="I28" t="n">
-        <v>1.412451388691732</v>
+        <v>1.41188838581708</v>
       </c>
       <c r="J28" t="n">
         <v>-1</v>
@@ -1985,19 +1985,19 @@
         <v>-0.01636413987360874</v>
       </c>
       <c r="O28" t="n">
-        <v>-0.006302886415383235</v>
+        <v>-0.006303082331273746</v>
       </c>
       <c r="P28" t="n">
         <v>0.01644350495297382</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0.006302886415383235</v>
+        <v>-0.006303082331273746</v>
       </c>
       <c r="R28" t="n">
-        <v>0.01014061853759058</v>
+        <v>0.01014042262170007</v>
       </c>
       <c r="S28" t="n">
-        <v>104.5116146994665</v>
+        <v>104.511605862765</v>
       </c>
     </row>
     <row r="29">
@@ -2017,16 +2017,16 @@
         <v>5.721368826915722</v>
       </c>
       <c r="F29" t="n">
-        <v>1.137780444392145</v>
+        <v>1.140808473244973</v>
       </c>
       <c r="G29" t="n">
-        <v>1.101421077071233</v>
+        <v>1.104485917898157</v>
       </c>
       <c r="H29" t="n">
-        <v>0.0384720685093613</v>
+        <v>0.03846169353777219</v>
       </c>
       <c r="I29" t="n">
-        <v>0.9450848038509821</v>
+        <v>0.9443826312833686</v>
       </c>
       <c r="J29" t="n">
         <v>0</v>
@@ -2044,19 +2044,19 @@
         <v>-0.02209273399248279</v>
       </c>
       <c r="O29" t="n">
-        <v>-0.0106149532987545</v>
+        <v>-0.01061485545752938</v>
       </c>
       <c r="P29" t="n">
         <v>0.02217209907184787</v>
       </c>
       <c r="Q29" t="n">
-        <v>-0.0106149532987545</v>
+        <v>-0.01061485545752938</v>
       </c>
       <c r="R29" t="n">
-        <v>0.01155714577309337</v>
+        <v>0.01155724361431849</v>
       </c>
       <c r="S29" t="n">
-        <v>105.7194706655296</v>
+        <v>105.7194719522446</v>
       </c>
     </row>
     <row r="30">
@@ -2076,16 +2076,16 @@
         <v>5.70919231456057</v>
       </c>
       <c r="F30" t="n">
-        <v>1.158187598110431</v>
+        <v>1.161209182556011</v>
       </c>
       <c r="G30" t="n">
-        <v>1.10423255662848</v>
+        <v>1.107295052894468</v>
       </c>
       <c r="H30" t="n">
-        <v>0.04051378084160917</v>
+        <v>0.04050090790453605</v>
       </c>
       <c r="I30" t="n">
-        <v>1.331770088131027</v>
+        <v>1.331183236401081</v>
       </c>
       <c r="J30" t="n">
         <v>-1</v>
@@ -2115,7 +2115,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S30" t="n">
-        <v>105.7278610997094</v>
+        <v>105.7278623865265</v>
       </c>
     </row>
     <row r="31">
@@ -2135,16 +2135,16 @@
         <v>5.713520469255783</v>
       </c>
       <c r="F31" t="n">
-        <v>1.171250942339261</v>
+        <v>1.174274817456477</v>
       </c>
       <c r="G31" t="n">
-        <v>1.109064715681815</v>
+        <v>1.112125631337779</v>
       </c>
       <c r="H31" t="n">
-        <v>0.04250870042499809</v>
+        <v>0.04249315892511238</v>
       </c>
       <c r="I31" t="n">
-        <v>1.462905853053935</v>
+        <v>1.462569215628952</v>
       </c>
       <c r="J31" t="n">
         <v>-1</v>
@@ -2174,7 +2174,7 @@
         <v>-0.01193528694799562</v>
       </c>
       <c r="S31" t="n">
-        <v>104.4659687390865</v>
+        <v>104.4659700105451</v>
       </c>
     </row>
     <row r="32">
@@ -2194,16 +2194,16 @@
         <v>5.711936800350696</v>
       </c>
       <c r="F32" t="n">
-        <v>1.171951733569247</v>
+        <v>1.174974770531245</v>
       </c>
       <c r="G32" t="n">
-        <v>1.113176842206665</v>
+        <v>1.116235616153625</v>
       </c>
       <c r="H32" t="n">
-        <v>0.04447042310042733</v>
+        <v>0.0444530700413392</v>
       </c>
       <c r="I32" t="n">
-        <v>1.321662517800895</v>
+        <v>1.321374526506153</v>
       </c>
       <c r="J32" t="n">
         <v>-1</v>
@@ -2233,7 +2233,7 @@
         <v>-0.001077513346820646</v>
       </c>
       <c r="S32" t="n">
-        <v>104.3534052634816</v>
+        <v>104.3534065335702</v>
       </c>
     </row>
     <row r="33">
@@ -2244,25 +2244,25 @@
         <v>189.5887756347656</v>
       </c>
       <c r="C33" t="n">
-        <v>314.570556640625</v>
+        <v>314.5705261230469</v>
       </c>
       <c r="D33" t="n">
         <v>5.24485738782994</v>
       </c>
       <c r="E33" t="n">
-        <v>5.75120839641801</v>
+        <v>5.751208299404545</v>
       </c>
       <c r="F33" t="n">
-        <v>1.154185399436435</v>
+        <v>1.157229289803813</v>
       </c>
       <c r="G33" t="n">
-        <v>1.116220950748195</v>
+        <v>1.119278455450549</v>
       </c>
       <c r="H33" t="n">
-        <v>0.04511748488006197</v>
+        <v>0.04510000228482146</v>
       </c>
       <c r="I33" t="n">
-        <v>0.8414575588413939</v>
+        <v>0.8414818720760165</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -2280,19 +2280,19 @@
         <v>0.01021829608122071</v>
       </c>
       <c r="O33" t="n">
-        <v>0.04005291957693391</v>
+        <v>0.04005281867780153</v>
       </c>
       <c r="P33" t="n">
         <v>-0.01013893100185563</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04005291957693391</v>
+        <v>0.04005281867780153</v>
       </c>
       <c r="R33" t="n">
-        <v>0.02991398857507828</v>
+        <v>0.0299138876759459</v>
       </c>
       <c r="S33" t="n">
-        <v>107.4750318363039</v>
+        <v>107.4750226152178</v>
       </c>
     </row>
     <row r="34">
@@ -2312,16 +2312,16 @@
         <v>5.740066355466205</v>
       </c>
       <c r="F34" t="n">
-        <v>1.171182941202269</v>
+        <v>1.174220865703784</v>
       </c>
       <c r="G34" t="n">
-        <v>1.119073280663917</v>
+        <v>1.122129424323693</v>
       </c>
       <c r="H34" t="n">
-        <v>0.04675238270422814</v>
+        <v>0.04673440527798898</v>
       </c>
       <c r="I34" t="n">
-        <v>1.11458833805361</v>
+        <v>1.114627244537225</v>
       </c>
       <c r="J34" t="n">
         <v>-1</v>
@@ -2339,7 +2339,7 @@
         <v>0.009113803019584088</v>
       </c>
       <c r="O34" t="n">
-        <v>-0.01108019831103446</v>
+        <v>-0.01108010237249346</v>
       </c>
       <c r="P34" t="n">
         <v>-0.0001984126984126984</v>
@@ -2351,7 +2351,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S34" t="n">
-        <v>107.4835616007354</v>
+        <v>107.4835523789174</v>
       </c>
     </row>
     <row r="35">
@@ -2371,16 +2371,16 @@
         <v>5.738170534486693</v>
       </c>
       <c r="F35" t="n">
-        <v>1.179295276880336</v>
+        <v>1.182332198020454</v>
       </c>
       <c r="G35" t="n">
-        <v>1.123225348809269</v>
+        <v>1.126279654608244</v>
       </c>
       <c r="H35" t="n">
-        <v>0.04828157129980546</v>
+        <v>0.04826350385738925</v>
       </c>
       <c r="I35" t="n">
-        <v>1.161311170320025</v>
+        <v>1.161385704151024</v>
       </c>
       <c r="J35" t="n">
         <v>-1</v>
@@ -2410,7 +2410,7 @@
         <v>-0.008680843620532563</v>
       </c>
       <c r="S35" t="n">
-        <v>106.5505136107015</v>
+        <v>106.5505044689367</v>
       </c>
     </row>
     <row r="36">
@@ -2421,25 +2421,25 @@
         <v>195.3217620849609</v>
       </c>
       <c r="C36" t="n">
-        <v>312.4932556152344</v>
+        <v>312.4932250976562</v>
       </c>
       <c r="D36" t="n">
         <v>5.274648260681339</v>
       </c>
       <c r="E36" t="n">
-        <v>5.744582886912311</v>
+        <v>5.744582789253949</v>
       </c>
       <c r="F36" t="n">
-        <v>1.188688809945255</v>
+        <v>1.191729194226566</v>
       </c>
       <c r="G36" t="n">
-        <v>1.127437800588806</v>
+        <v>1.130490339451421</v>
       </c>
       <c r="H36" t="n">
-        <v>0.05019371126094478</v>
+        <v>0.0501759543949344</v>
       </c>
       <c r="I36" t="n">
-        <v>1.220292499154316</v>
+        <v>1.220482111673142</v>
       </c>
       <c r="J36" t="n">
         <v>-1</v>
@@ -2457,19 +2457,19 @@
         <v>0.01405227603538939</v>
       </c>
       <c r="O36" t="n">
-        <v>0.00643295557210255</v>
+        <v>0.006432857285513016</v>
       </c>
       <c r="P36" t="n">
         <v>-0.01397291095602431</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.00643295557210255</v>
+        <v>0.006432857285513016</v>
       </c>
       <c r="R36" t="n">
-        <v>-0.007539955383921758</v>
+        <v>-0.007540053670511292</v>
       </c>
       <c r="S36" t="n">
-        <v>105.7471274919429</v>
+        <v>105.7471079466209</v>
       </c>
     </row>
     <row r="37">
@@ -2480,25 +2480,25 @@
         <v>184.6647644042969</v>
       </c>
       <c r="C37" t="n">
-        <v>306.9804077148438</v>
+        <v>306.9804382324219</v>
       </c>
       <c r="D37" t="n">
         <v>5.218542096966353</v>
       </c>
       <c r="E37" t="n">
-        <v>5.726783927032285</v>
+        <v>5.726784026444416</v>
       </c>
       <c r="F37" t="n">
-        <v>1.145242543348432</v>
+        <v>1.148273367481272</v>
       </c>
       <c r="G37" t="n">
-        <v>1.128843398081852</v>
+        <v>1.131893579999935</v>
       </c>
       <c r="H37" t="n">
-        <v>0.0502834181170008</v>
+        <v>0.05026563173159222</v>
       </c>
       <c r="I37" t="n">
-        <v>0.3261342581847064</v>
+        <v>0.3258645503313626</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2516,19 +2516,19 @@
         <v>-0.05456124072866231</v>
       </c>
       <c r="O37" t="n">
-        <v>-0.01764149402052528</v>
+        <v>-0.01764130042663037</v>
       </c>
       <c r="P37" t="n">
         <v>0.05464060580802739</v>
       </c>
       <c r="Q37" t="n">
-        <v>-0.01764149402052528</v>
+        <v>-0.01764130042663037</v>
       </c>
       <c r="R37" t="n">
-        <v>0.03699911178750211</v>
+        <v>0.03699930538139702</v>
       </c>
       <c r="S37" t="n">
-        <v>109.6596772832245</v>
+        <v>109.6596774867374</v>
       </c>
     </row>
     <row r="38">
@@ -2548,16 +2548,16 @@
         <v>5.740932893433766</v>
       </c>
       <c r="F38" t="n">
-        <v>1.092640372282307</v>
+        <v>1.095678755398194</v>
       </c>
       <c r="G38" t="n">
-        <v>1.127597392804254</v>
+        <v>1.130645413456445</v>
       </c>
       <c r="H38" t="n">
-        <v>0.05088290211111998</v>
+        <v>0.05086607800958882</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.6870091734470395</v>
+        <v>-0.6874258725364913</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2575,7 +2575,7 @@
         <v>-0.04164634665296119</v>
       </c>
       <c r="O38" t="n">
-        <v>0.01424953678915108</v>
+        <v>0.01424943596044792</v>
       </c>
       <c r="P38" t="n">
         <v>-0.0001984126984126984</v>
@@ -2587,7 +2587,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S38" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="39">
@@ -2607,16 +2607,16 @@
         <v>5.723982150556365</v>
       </c>
       <c r="F39" t="n">
-        <v>1.134114921668485</v>
+        <v>1.137144333620292</v>
       </c>
       <c r="G39" t="n">
-        <v>1.12875852996648</v>
+        <v>1.131803963572116</v>
       </c>
       <c r="H39" t="n">
-        <v>0.05074641497452159</v>
+        <v>0.0507300558799935</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1055521203752783</v>
+        <v>0.105270336401955</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2646,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="S39" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="40">
@@ -2666,16 +2666,16 @@
         <v>5.714344279418622</v>
       </c>
       <c r="F40" t="n">
-        <v>1.12756403510678</v>
+        <v>1.130588346224719</v>
       </c>
       <c r="G40" t="n">
-        <v>1.131651136767202</v>
+        <v>1.134693289676183</v>
       </c>
       <c r="H40" t="n">
-        <v>0.04881563206320536</v>
+        <v>0.04880168999651958</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.08372526356166977</v>
+        <v>-0.08411478069216304</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2705,7 +2705,7 @@
         <v>-0</v>
       </c>
       <c r="S40" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="41">
@@ -2725,16 +2725,16 @@
         <v>5.712861012783621</v>
       </c>
       <c r="F41" t="n">
-        <v>1.14508916510726</v>
+        <v>1.148112691207784</v>
       </c>
       <c r="G41" t="n">
-        <v>1.136445950830922</v>
+        <v>1.139485088861262</v>
       </c>
       <c r="H41" t="n">
-        <v>0.04483758117768515</v>
+        <v>0.04482648096364234</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1927671843422123</v>
+        <v>0.1924666438465001</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
@@ -2764,7 +2764,7 @@
         <v>0</v>
       </c>
       <c r="S41" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="42">
@@ -2775,25 +2775,25 @@
         <v>183.1166381835938</v>
       </c>
       <c r="C42" t="n">
-        <v>300.4888916015625</v>
+        <v>300.4888610839844</v>
       </c>
       <c r="D42" t="n">
         <v>5.210123316932725</v>
       </c>
       <c r="E42" t="n">
-        <v>5.705410786907837</v>
+        <v>5.705410685348077</v>
       </c>
       <c r="F42" t="n">
-        <v>1.152025873825273</v>
+        <v>1.155045529083878</v>
       </c>
       <c r="G42" t="n">
-        <v>1.142617248325636</v>
+        <v>1.145653699413875</v>
       </c>
       <c r="H42" t="n">
-        <v>0.03702633149706917</v>
+        <v>0.03701818099798889</v>
       </c>
       <c r="I42" t="n">
-        <v>0.2541063378201784</v>
+        <v>0.2537085674337692</v>
       </c>
       <c r="J42" t="n">
         <v>0</v>
@@ -2811,7 +2811,7 @@
         <v>0.001638915171032762</v>
       </c>
       <c r="O42" t="n">
-        <v>-0.007422541736676336</v>
+        <v>-0.007422642542599611</v>
       </c>
       <c r="P42" t="n">
         <v>0</v>
@@ -2823,7 +2823,7 @@
         <v>0</v>
       </c>
       <c r="S42" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="43">
@@ -2843,16 +2843,16 @@
         <v>5.697536098237152</v>
       </c>
       <c r="F43" t="n">
-        <v>1.127056538613487</v>
+        <v>1.130071954017984</v>
       </c>
       <c r="G43" t="n">
-        <v>1.148015923190077</v>
+        <v>1.151049617939286</v>
       </c>
       <c r="H43" t="n">
-        <v>0.02344821487991332</v>
+        <v>0.02344620066875547</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.8938584316090068</v>
+        <v>-0.8947148502937247</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
@@ -2870,7 +2870,7 @@
         <v>-0.03010783008903128</v>
       </c>
       <c r="O43" t="n">
-        <v>-0.007843764535739872</v>
+        <v>-0.007843663772585718</v>
       </c>
       <c r="P43" t="n">
         <v>-0</v>
@@ -2882,7 +2882,7 @@
         <v>-0</v>
       </c>
       <c r="S43" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="44">
@@ -2902,16 +2902,16 @@
         <v>5.724163671495992</v>
       </c>
       <c r="F44" t="n">
-        <v>1.134916940378131</v>
+        <v>1.137946448399718</v>
       </c>
       <c r="G44" t="n">
-        <v>1.149106594438974</v>
+        <v>1.152138919643602</v>
       </c>
       <c r="H44" t="n">
-        <v>0.02221364291268626</v>
+        <v>0.02221363633881</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.6387810462524249</v>
+        <v>-0.6389080575289837</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
@@ -2941,7 +2941,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="45">
@@ -2961,16 +2961,16 @@
         <v>5.726380928450948</v>
       </c>
       <c r="F45" t="n">
-        <v>1.14487991804154</v>
+        <v>1.1479105995442</v>
       </c>
       <c r="G45" t="n">
-        <v>1.149622631506656</v>
+        <v>1.15265352644281</v>
       </c>
       <c r="H45" t="n">
-        <v>0.02197652364951244</v>
+        <v>0.02197750739098813</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.2158081751579287</v>
+        <v>-0.2158082267579652</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
         <v>0</v>
       </c>
       <c r="S45" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="46">
@@ -3020,16 +3020,16 @@
         <v>5.731772886030789</v>
       </c>
       <c r="F46" t="n">
-        <v>1.147895050869251</v>
+        <v>1.150928586060184</v>
       </c>
       <c r="G46" t="n">
-        <v>1.150050578549441</v>
+        <v>1.153080658446157</v>
       </c>
       <c r="H46" t="n">
-        <v>0.02184863416137732</v>
+        <v>0.02185009835864581</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.0986573194584439</v>
+        <v>-0.09849257200809702</v>
       </c>
       <c r="J46" t="n">
         <v>0</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="S46" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="47">
@@ -3079,16 +3079,16 @@
         <v>5.714949142745352</v>
       </c>
       <c r="F47" t="n">
-        <v>1.144204286403078</v>
+        <v>1.147228917644341</v>
       </c>
       <c r="G47" t="n">
-        <v>1.149034159759707</v>
+        <v>1.152063623551148</v>
       </c>
       <c r="H47" t="n">
-        <v>0.02161101049974041</v>
+        <v>0.02161229542891531</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.2234913243268649</v>
+        <v>-0.2237016388522243</v>
       </c>
       <c r="J47" t="n">
         <v>0</v>
@@ -3118,7 +3118,7 @@
         <v>-0</v>
       </c>
       <c r="S47" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="48">
@@ -3138,16 +3138,16 @@
         <v>5.710756593323133</v>
       </c>
       <c r="F48" t="n">
-        <v>1.131280179283359</v>
+        <v>1.134302591621942</v>
       </c>
       <c r="G48" t="n">
-        <v>1.147971648540138</v>
+        <v>1.151000545592392</v>
       </c>
       <c r="H48" t="n">
-        <v>0.02194980064767979</v>
+        <v>0.02195130115996064</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.7604383076045458</v>
+        <v>-0.7606817404020794</v>
       </c>
       <c r="J48" t="n">
         <v>0</v>
@@ -3177,7 +3177,7 @@
         <v>-0</v>
       </c>
       <c r="S48" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="49">
@@ -3197,16 +3197,16 @@
         <v>5.721549023996647</v>
       </c>
       <c r="F49" t="n">
-        <v>1.139946724926748</v>
+        <v>1.142974849148705</v>
       </c>
       <c r="G49" t="n">
-        <v>1.148079962566868</v>
+        <v>1.151108864387578</v>
       </c>
       <c r="H49" t="n">
-        <v>0.02190215723505423</v>
+        <v>0.02190365462793087</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.3713441353211905</v>
+        <v>-0.3713542501031262</v>
       </c>
       <c r="J49" t="n">
         <v>0</v>
@@ -3236,7 +3236,7 @@
         <v>0</v>
       </c>
       <c r="S49" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="50">
@@ -3256,16 +3256,16 @@
         <v>5.738938545760967</v>
       </c>
       <c r="F50" t="n">
-        <v>1.120512348856322</v>
+        <v>1.123549676465656</v>
       </c>
       <c r="G50" t="n">
-        <v>1.146196200104163</v>
+        <v>1.14922588908306</v>
       </c>
       <c r="H50" t="n">
-        <v>0.02259625393793602</v>
+        <v>0.02259740568132087</v>
       </c>
       <c r="I50" t="n">
-        <v>-1.136641999084675</v>
+        <v>-1.136246035474281</v>
       </c>
       <c r="J50" t="n">
         <v>1</v>
@@ -3295,7 +3295,7 @@
         <v>0</v>
       </c>
       <c r="S50" t="n">
-        <v>109.6683804322153</v>
+        <v>109.6683806357443</v>
       </c>
     </row>
     <row r="51">
@@ -3315,16 +3315,16 @@
         <v>5.728495630575953</v>
       </c>
       <c r="F51" t="n">
-        <v>1.119494738634745</v>
+        <v>1.122526539341436</v>
       </c>
       <c r="G51" t="n">
-        <v>1.143608389918937</v>
+        <v>1.146638475177308</v>
       </c>
       <c r="H51" t="n">
-        <v>0.02253945762851689</v>
+        <v>0.02254086858711838</v>
       </c>
       <c r="I51" t="n">
-        <v>-1.069841683044033</v>
+        <v>-1.069698611776291</v>
       </c>
       <c r="J51" t="n">
         <v>1</v>
@@ -3354,7 +3354,7 @@
         <v>0.001978778487409683</v>
       </c>
       <c r="S51" t="n">
-        <v>109.8853898641636</v>
+        <v>109.8853900680954</v>
       </c>
     </row>
     <row r="52">
@@ -3374,16 +3374,16 @@
         <v>5.726673971164641</v>
       </c>
       <c r="F52" t="n">
-        <v>1.11053849302672</v>
+        <v>1.11356932962195</v>
       </c>
       <c r="G52" t="n">
-        <v>1.140537727891811</v>
+        <v>1.143568203131843</v>
       </c>
       <c r="H52" t="n">
-        <v>0.02265787826162289</v>
+        <v>0.02265974371723628</v>
       </c>
       <c r="I52" t="n">
-        <v>-1.324009005552044</v>
+        <v>-1.32388405995406</v>
       </c>
       <c r="J52" t="n">
         <v>1</v>
@@ -3413,7 +3413,7 @@
         <v>-0.00845893232777757</v>
       </c>
       <c r="S52" t="n">
-        <v>108.9558767874912</v>
+        <v>108.955876989698</v>
       </c>
     </row>
     <row r="53">
@@ -3433,16 +3433,16 @@
         <v>5.706513118053733</v>
       </c>
       <c r="F53" t="n">
-        <v>1.091509632840355</v>
+        <v>1.094529799323805</v>
       </c>
       <c r="G53" t="n">
-        <v>1.137403939562007</v>
+        <v>1.140433228607843</v>
       </c>
       <c r="H53" t="n">
-        <v>0.02489482304977883</v>
+        <v>0.02489704503174741</v>
       </c>
       <c r="I53" t="n">
-        <v>-1.843528135543815</v>
+        <v>-1.843730017980225</v>
       </c>
       <c r="J53" t="n">
         <v>1</v>
@@ -3472,7 +3472,7 @@
         <v>-0.0129384942183441</v>
       </c>
       <c r="S53" t="n">
-        <v>107.5461518056216</v>
+        <v>107.5461520052121</v>
       </c>
     </row>
     <row r="54">
@@ -3492,16 +3492,16 @@
         <v>5.710028592673332</v>
       </c>
       <c r="F54" t="n">
-        <v>1.105889676364086</v>
+        <v>1.108911703409038</v>
       </c>
       <c r="G54" t="n">
-        <v>1.134139276320097</v>
+        <v>1.137167770493106</v>
       </c>
       <c r="H54" t="n">
-        <v>0.02451021203965659</v>
+        <v>0.0245122224843188</v>
       </c>
       <c r="I54" t="n">
-        <v>-1.152564486602757</v>
+        <v>-1.152733788302738</v>
       </c>
       <c r="J54" t="n">
         <v>1</v>
@@ -3531,7 +3531,7 @@
         <v>0.01342275578000645</v>
       </c>
       <c r="S54" t="n">
-        <v>108.989717536388</v>
+        <v>108.9897177386576</v>
       </c>
     </row>
     <row r="55">
@@ -3551,16 +3551,16 @@
         <v>5.670799921537744</v>
       </c>
       <c r="F55" t="n">
-        <v>1.131283590703644</v>
+        <v>1.134284856012786</v>
       </c>
       <c r="G55" t="n">
-        <v>1.131738692011263</v>
+        <v>1.134765403392723</v>
       </c>
       <c r="H55" t="n">
-        <v>0.02208606829704957</v>
+        <v>0.02208737469761235</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.02060580912355634</v>
+        <v>-0.02175665449223677</v>
       </c>
       <c r="J55" t="n">
         <v>0</v>
@@ -3590,7 +3590,7 @@
         <v>0.03588463775490384</v>
       </c>
       <c r="S55" t="n">
-        <v>112.9007740691905</v>
+        <v>112.9007742787185</v>
       </c>
     </row>
     <row r="56">
@@ -3610,16 +3610,16 @@
         <v>5.672485518208908</v>
       </c>
       <c r="F56" t="n">
-        <v>1.149753011322602</v>
+        <v>1.152755168732132</v>
       </c>
       <c r="G56" t="n">
-        <v>1.12979190208013</v>
+        <v>1.132816702118001</v>
       </c>
       <c r="H56" t="n">
-        <v>0.01817096265221098</v>
+        <v>0.01816879881506655</v>
       </c>
       <c r="I56" t="n">
-        <v>1.098516882375687</v>
+        <v>1.097401474752283</v>
       </c>
       <c r="J56" t="n">
         <v>-1</v>
@@ -3649,7 +3649,7 @@
         <v>-7.936507936507937e-05</v>
       </c>
       <c r="S56" t="n">
-        <v>112.8918136902961</v>
+        <v>112.8918138998075</v>
       </c>
     </row>
     <row r="57">
@@ -3669,16 +3669,16 @@
         <v>5.63747285479881</v>
       </c>
       <c r="F57" t="n">
-        <v>1.132126221236463</v>
+        <v>1.135109848228147</v>
       </c>
       <c r="G57" t="n">
-        <v>1.129136085974532</v>
+        <v>1.132158526155345</v>
       </c>
       <c r="H57" t="n">
-        <v>0.01781722795127691</v>
+        <v>0.01781437305607451</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1678226977904937</v>
+        <v>0.1656708357634964</v>
       </c>
       <c r="J57" t="n">
         <v>0</v>
@@ -3708,7 +3708,7 @@
         <v>0.007231769435414481</v>
       </c>
       <c r="S57" t="n">
-        <v>113.7082212580501</v>
+        <v>113.7082214690766</v>
       </c>
     </row>
     <row r="58">
@@ -3728,16 +3728,16 @@
         <v>5.613771107697508</v>
       </c>
       <c r="F58" t="n">
-        <v>1.127021190296901</v>
+        <v>1.129992273162125</v>
       </c>
       <c r="G58" t="n">
-        <v>1.130855126875262</v>
+        <v>1.133874202043541</v>
       </c>
       <c r="H58" t="n">
-        <v>0.01563574221715024</v>
+        <v>0.01563520649840658</v>
       </c>
       <c r="I58" t="n">
-        <v>-0.2452033632375522</v>
+        <v>-0.248281267139721</v>
       </c>
       <c r="J58" t="n">
         <v>0</v>
@@ -3767,7 +3767,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S58" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="59">
@@ -3787,16 +3787,16 @@
         <v>5.610704481843535</v>
       </c>
       <c r="F59" t="n">
-        <v>1.115074922661524</v>
+        <v>1.118044382518016</v>
       </c>
       <c r="G59" t="n">
-        <v>1.129903126924913</v>
+        <v>1.132919204488427</v>
       </c>
       <c r="H59" t="n">
-        <v>0.0160021622942953</v>
+        <v>0.01600391889800488</v>
       </c>
       <c r="I59" t="n">
-        <v>-0.9266375375205114</v>
+        <v>-0.929448722229246</v>
       </c>
       <c r="J59" t="n">
         <v>0</v>
@@ -3826,7 +3826,7 @@
         <v>-0</v>
       </c>
       <c r="S59" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="60">
@@ -3846,16 +3846,16 @@
         <v>5.66083438890224</v>
       </c>
       <c r="F60" t="n">
-        <v>1.13379519218443</v>
+        <v>1.136791183245177</v>
       </c>
       <c r="G60" t="n">
-        <v>1.130214684778796</v>
+        <v>1.13322934633945</v>
       </c>
       <c r="H60" t="n">
-        <v>0.01601487831146685</v>
+        <v>0.01601646938832609</v>
       </c>
       <c r="I60" t="n">
-        <v>0.2235738128007271</v>
+        <v>0.2223858966273167</v>
       </c>
       <c r="J60" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         <v>0</v>
       </c>
       <c r="S60" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="61">
@@ -3905,16 +3905,16 @@
         <v>5.694447350642657</v>
       </c>
       <c r="F61" t="n">
-        <v>1.117598296018657</v>
+        <v>1.120612076706512</v>
       </c>
       <c r="G61" t="n">
-        <v>1.128840141324366</v>
+        <v>1.131854315614387</v>
       </c>
       <c r="H61" t="n">
-        <v>0.01584993097350644</v>
+        <v>0.01585109308915431</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.709267776907046</v>
+        <v>-0.7092406084957634</v>
       </c>
       <c r="J61" t="n">
         <v>0</v>
@@ -3944,7 +3944,7 @@
         <v>0</v>
       </c>
       <c r="S61" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="62">
@@ -3964,16 +3964,16 @@
         <v>5.688985012996693</v>
       </c>
       <c r="F62" t="n">
-        <v>1.130771590634669</v>
+        <v>1.13378248038567</v>
       </c>
       <c r="G62" t="n">
-        <v>1.127777427164836</v>
+        <v>1.130791163179476</v>
       </c>
       <c r="H62" t="n">
-        <v>0.0148974582829823</v>
+        <v>0.01489819039788359</v>
       </c>
       <c r="I62" t="n">
-        <v>0.2009848534534332</v>
+        <v>0.200783929209192</v>
       </c>
       <c r="J62" t="n">
         <v>0</v>
@@ -4003,7 +4003,7 @@
         <v>0</v>
       </c>
       <c r="S62" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="63">
@@ -4023,16 +4023,16 @@
         <v>5.703151986226595</v>
       </c>
       <c r="F63" t="n">
-        <v>1.122103361245271</v>
+        <v>1.12512174885299</v>
       </c>
       <c r="G63" t="n">
-        <v>1.127529768296425</v>
+        <v>1.130543652921226</v>
       </c>
       <c r="H63" t="n">
-        <v>0.01495114790175834</v>
+        <v>0.01495179136588275</v>
       </c>
       <c r="I63" t="n">
-        <v>-0.362942503599702</v>
+        <v>-0.3626257172507077</v>
       </c>
       <c r="J63" t="n">
         <v>0</v>
@@ -4062,7 +4062,7 @@
         <v>0</v>
       </c>
       <c r="S63" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="64">
@@ -4082,16 +4082,16 @@
         <v>5.721221686860314</v>
       </c>
       <c r="F64" t="n">
-        <v>1.111837099701513</v>
+        <v>1.114865050680611</v>
       </c>
       <c r="G64" t="n">
-        <v>1.126375776262594</v>
+        <v>1.129389583035271</v>
       </c>
       <c r="H64" t="n">
-        <v>0.01523889627168938</v>
+        <v>0.01523836031588584</v>
       </c>
       <c r="I64" t="n">
-        <v>-0.9540504969569495</v>
+        <v>-0.9531558549326764</v>
       </c>
       <c r="J64" t="n">
         <v>0</v>
@@ -4121,7 +4121,7 @@
         <v>0</v>
       </c>
       <c r="S64" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="65">
@@ -4141,16 +4141,16 @@
         <v>5.759313628223341</v>
       </c>
       <c r="F65" t="n">
-        <v>1.106844369404419</v>
+        <v>1.109892480506207</v>
       </c>
       <c r="G65" t="n">
-        <v>1.124473998830738</v>
+        <v>1.127488677083372</v>
       </c>
       <c r="H65" t="n">
-        <v>0.01518134706401714</v>
+        <v>0.01517751966936278</v>
       </c>
       <c r="I65" t="n">
-        <v>-1.161269112153095</v>
+        <v>-1.159359168065153</v>
       </c>
       <c r="J65" t="n">
         <v>1</v>
@@ -4180,7 +4180,7 @@
         <v>0</v>
       </c>
       <c r="S65" t="n">
-        <v>113.7172457200547</v>
+        <v>113.717245931098</v>
       </c>
     </row>
     <row r="66">
@@ -4200,16 +4200,16 @@
         <v>5.762993912430139</v>
       </c>
       <c r="F66" t="n">
-        <v>1.114227021463163</v>
+        <v>1.117277080351766</v>
       </c>
       <c r="G66" t="n">
-        <v>1.122790597360434</v>
+        <v>1.125806101797951</v>
       </c>
       <c r="H66" t="n">
-        <v>0.01428796094483416</v>
+        <v>0.01428103480348655</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.5993560543967172</v>
+        <v>-0.5972271311951984</v>
       </c>
       <c r="J66" t="n">
         <v>0</v>
@@ -4239,7 +4239,7 @@
         <v>0.006363439875416654</v>
       </c>
       <c r="S66" t="n">
-        <v>114.4408785759923</v>
+        <v>114.4408787883785</v>
       </c>
     </row>
     <row r="67">
@@ -4259,16 +4259,16 @@
         <v>5.759061472992551</v>
       </c>
       <c r="F67" t="n">
-        <v>1.142364985564678</v>
+        <v>1.145412963213556</v>
       </c>
       <c r="G67" t="n">
-        <v>1.122698632318514</v>
+        <v>1.125715304076411</v>
       </c>
       <c r="H67" t="n">
-        <v>0.01414811159993049</v>
+        <v>0.01414276500429436</v>
       </c>
       <c r="I67" t="n">
-        <v>1.390033794069074</v>
+        <v>1.392772851077132</v>
       </c>
       <c r="J67" t="n">
         <v>-1</v>
@@ -4298,7 +4298,7 @@
         <v>-7.936507936507937e-05</v>
       </c>
       <c r="S67" t="n">
-        <v>114.4317959665815</v>
+        <v>114.4317961789508</v>
       </c>
     </row>
     <row r="68">
@@ -4318,16 +4318,16 @@
         <v>5.771809262772875</v>
       </c>
       <c r="F68" t="n">
-        <v>1.136896253028241</v>
+        <v>1.139950977432386</v>
       </c>
       <c r="G68" t="n">
-        <v>1.122979436005757</v>
+        <v>1.125997723366934</v>
       </c>
       <c r="H68" t="n">
-        <v>0.01438120968180669</v>
+        <v>0.01437771651725862</v>
       </c>
       <c r="I68" t="n">
-        <v>0.9677083729673678</v>
+        <v>0.9704777562350514</v>
       </c>
       <c r="J68" t="n">
         <v>0</v>
@@ -4357,7 +4357,7 @@
         <v>0.009224497122282127</v>
       </c>
       <c r="S68" t="n">
-        <v>115.4873717391728</v>
+        <v>115.4873719535012</v>
       </c>
     </row>
     <row r="69">
@@ -4377,16 +4377,16 @@
         <v>5.807275066409984</v>
       </c>
       <c r="F69" t="n">
-        <v>1.148997875745103</v>
+        <v>1.152071370391116</v>
       </c>
       <c r="G69" t="n">
-        <v>1.123431993546675</v>
+        <v>1.126452549429054</v>
       </c>
       <c r="H69" t="n">
-        <v>0.01506920665133907</v>
+        <v>0.01507024053724546</v>
       </c>
       <c r="I69" t="n">
-        <v>1.696564576354485</v>
+        <v>1.699960985940896</v>
       </c>
       <c r="J69" t="n">
         <v>-1</v>
@@ -4416,7 +4416,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S69" t="n">
-        <v>115.4965374035966</v>
+        <v>115.4965376179419</v>
       </c>
     </row>
     <row r="70">
@@ -4436,16 +4436,16 @@
         <v>5.819841839592116</v>
       </c>
       <c r="F70" t="n">
-        <v>1.151997516519829</v>
+        <v>1.155077662118252</v>
       </c>
       <c r="G70" t="n">
-        <v>1.125006251929851</v>
+        <v>1.128028948711684</v>
       </c>
       <c r="H70" t="n">
-        <v>0.01633922916011205</v>
+        <v>0.01634561032046354</v>
       </c>
       <c r="I70" t="n">
-        <v>1.651930107931327</v>
+        <v>1.654799843888677</v>
       </c>
       <c r="J70" t="n">
         <v>-1</v>
@@ -4475,7 +4475,7 @@
         <v>0.000636492807590594</v>
       </c>
       <c r="S70" t="n">
-        <v>115.5700501189556</v>
+        <v>115.5700503334374</v>
       </c>
     </row>
     <row r="71">
@@ -4495,16 +4495,16 @@
         <v>5.816573506443499</v>
       </c>
       <c r="F71" t="n">
-        <v>1.151703995238876</v>
+        <v>1.154782411075177</v>
       </c>
       <c r="G71" t="n">
-        <v>1.126616714760057</v>
+        <v>1.129641742298371</v>
       </c>
       <c r="H71" t="n">
-        <v>0.01732500275663296</v>
+        <v>0.0173354667398984</v>
       </c>
       <c r="I71" t="n">
-        <v>1.448039046874823</v>
+        <v>1.45024470087926</v>
       </c>
       <c r="J71" t="n">
         <v>-1</v>
@@ -4534,7 +4534,7 @@
         <v>-0.0005688630857300534</v>
       </c>
       <c r="S71" t="n">
-        <v>115.5043065836269</v>
+        <v>115.5043067979867</v>
       </c>
     </row>
     <row r="72">
@@ -4554,16 +4554,16 @@
         <v>5.833277526334015</v>
       </c>
       <c r="F72" t="n">
-        <v>1.156471971321859</v>
+        <v>1.159559227744342</v>
       </c>
       <c r="G72" t="n">
-        <v>1.128913388674814</v>
+        <v>1.131941237204491</v>
       </c>
       <c r="H72" t="n">
-        <v>0.01810828771974418</v>
+        <v>0.01812359567614568</v>
       </c>
       <c r="I72" t="n">
-        <v>1.52187678225351</v>
+        <v>1.523869271493546</v>
       </c>
       <c r="J72" t="n">
         <v>-1</v>
@@ -4593,7 +4593,7 @@
         <v>0.0001352356394574532</v>
       </c>
       <c r="S72" t="n">
-        <v>115.5199268823878</v>
+        <v>115.5199270967766</v>
       </c>
     </row>
     <row r="73">
@@ -4613,16 +4613,16 @@
         <v>5.820731377074562</v>
       </c>
       <c r="F73" t="n">
-        <v>1.167278116462918</v>
+        <v>1.170358732848183</v>
       </c>
       <c r="G73" t="n">
-        <v>1.132701812855942</v>
+        <v>1.13573268388071</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0177942329967179</v>
+        <v>0.01781427076321311</v>
       </c>
       <c r="I73" t="n">
-        <v>1.943118515608581</v>
+        <v>1.943725310326892</v>
       </c>
       <c r="J73" t="n">
         <v>-1</v>
@@ -4652,7 +4652,7 @@
         <v>-0.01427260599046691</v>
       </c>
       <c r="S73" t="n">
-        <v>113.871156481948</v>
+        <v>113.8711566932769</v>
       </c>
     </row>
     <row r="74">
@@ -4672,16 +4672,16 @@
         <v>5.805410967834648</v>
       </c>
       <c r="F74" t="n">
-        <v>1.167327682464157</v>
+        <v>1.170400190537824</v>
       </c>
       <c r="G74" t="n">
-        <v>1.135773713160946</v>
+        <v>1.138807108237149</v>
       </c>
       <c r="H74" t="n">
-        <v>0.01821998408930763</v>
+        <v>0.01824258455772082</v>
       </c>
       <c r="I74" t="n">
-        <v>1.731832977929323</v>
+        <v>1.731831484771907</v>
       </c>
       <c r="J74" t="n">
         <v>-1</v>
@@ -4711,7 +4711,7 @@
         <v>-0.004335496604960286</v>
       </c>
       <c r="S74" t="n">
-        <v>113.3774684696176</v>
+        <v>113.3774686800302</v>
       </c>
     </row>
     <row r="75">
@@ -4731,16 +4731,16 @@
         <v>5.826346543406457</v>
       </c>
       <c r="F75" t="n">
-        <v>1.165459465951879</v>
+        <v>1.16854305415843</v>
       </c>
       <c r="G75" t="n">
-        <v>1.137482506923358</v>
+        <v>1.140520018144431</v>
       </c>
       <c r="H75" t="n">
-        <v>0.019344619516754</v>
+        <v>0.01936918393956539</v>
       </c>
       <c r="I75" t="n">
-        <v>1.446239818999344</v>
+        <v>1.446784547115413</v>
       </c>
       <c r="J75" t="n">
         <v>-1</v>
@@ -4770,7 +4770,7 @@
         <v>0.008127796280000333</v>
       </c>
       <c r="S75" t="n">
-        <v>114.2989774360808</v>
+        <v>114.2989776482036</v>
       </c>
     </row>
     <row r="76">
@@ -4790,16 +4790,16 @@
         <v>5.825078484064047</v>
       </c>
       <c r="F76" t="n">
-        <v>1.152137240927295</v>
+        <v>1.15522015801468</v>
       </c>
       <c r="G76" t="n">
-        <v>1.137601718403592</v>
+        <v>1.140643267608558</v>
       </c>
       <c r="H76" t="n">
-        <v>0.0194313684320313</v>
+        <v>0.0194587713098647</v>
       </c>
       <c r="I76" t="n">
-        <v>0.7480442036054273</v>
+        <v>0.7491166926213916</v>
       </c>
       <c r="J76" t="n">
         <v>0</v>
@@ -4829,7 +4829,7 @@
         <v>0.01293558377350952</v>
       </c>
       <c r="S76" t="n">
-        <v>115.7775014339317</v>
+        <v>115.7775016487985</v>
       </c>
     </row>
     <row r="77">
@@ -4849,16 +4849,16 @@
         <v>5.841206605238948</v>
       </c>
       <c r="F77" t="n">
-        <v>1.182985314199811</v>
+        <v>1.186076767079546</v>
       </c>
       <c r="G77" t="n">
-        <v>1.14014467305176</v>
+        <v>1.143191613551128</v>
       </c>
       <c r="H77" t="n">
-        <v>0.02185399016318637</v>
+        <v>0.02188238253190911</v>
       </c>
       <c r="I77" t="n">
-        <v>1.960312090751177</v>
+        <v>1.959802753008383</v>
       </c>
       <c r="J77" t="n">
         <v>-1</v>
@@ -4888,7 +4888,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S77" t="n">
-        <v>115.7866901245217</v>
+        <v>115.7866903394055</v>
       </c>
     </row>
     <row r="78">
@@ -4908,16 +4908,16 @@
         <v>5.858306968534851</v>
       </c>
       <c r="F78" t="n">
-        <v>1.210085499365652</v>
+        <v>1.213186002595927</v>
       </c>
       <c r="G78" t="n">
-        <v>1.144297888505197</v>
+        <v>1.147351300022818</v>
       </c>
       <c r="H78" t="n">
-        <v>0.02660515408000967</v>
+        <v>0.02663285141994259</v>
       </c>
       <c r="I78" t="n">
-        <v>2.472739329477735</v>
+        <v>2.471935938628493</v>
       </c>
       <c r="J78" t="n">
         <v>-1</v>
@@ -4947,7 +4947,7 @@
         <v>-0.02279676564269106</v>
       </c>
       <c r="S78" t="n">
-        <v>113.1471280852101</v>
+        <v>113.1471282951952</v>
       </c>
     </row>
     <row r="79">
@@ -4967,16 +4967,16 @@
         <v>5.85670725340159</v>
       </c>
       <c r="F79" t="n">
-        <v>1.195214827366352</v>
+        <v>1.198314483948958</v>
       </c>
       <c r="G79" t="n">
-        <v>1.148304883740439</v>
+        <v>1.151364805094366</v>
       </c>
       <c r="H79" t="n">
-        <v>0.02797205651019888</v>
+        <v>0.02799723009179725</v>
       </c>
       <c r="I79" t="n">
-        <v>1.677028773655226</v>
+        <v>1.676940136601155</v>
       </c>
       <c r="J79" t="n">
         <v>-1</v>
@@ -5006,7 +5006,7 @@
         <v>0.01436197789513645</v>
       </c>
       <c r="S79" t="n">
-        <v>114.772144637668</v>
+        <v>114.772144850669</v>
       </c>
     </row>
     <row r="80">
@@ -5026,16 +5026,16 @@
         <v>5.857164600990844</v>
       </c>
       <c r="F80" t="n">
-        <v>1.176329272979323</v>
+        <v>1.179429171612692</v>
       </c>
       <c r="G80" t="n">
-        <v>1.150431587780183</v>
+        <v>1.153496704512742</v>
       </c>
       <c r="H80" t="n">
-        <v>0.02842410097128862</v>
+        <v>0.02844881948815059</v>
       </c>
       <c r="I80" t="n">
-        <v>0.9111171264589403</v>
+        <v>0.9115480911519597</v>
       </c>
       <c r="J80" t="n">
         <v>0</v>
@@ -5065,7 +5065,7 @@
         <v>0.01892589237923432</v>
       </c>
       <c r="S80" t="n">
-        <v>116.9443098952144</v>
+        <v>116.9443101122467</v>
       </c>
     </row>
     <row r="81">
@@ -5085,16 +5085,16 @@
         <v>5.952126560232704</v>
       </c>
       <c r="F81" t="n">
-        <v>1.061420856175275</v>
+        <v>1.064571013332646</v>
       </c>
       <c r="G81" t="n">
-        <v>1.147622715788014</v>
+        <v>1.150694651344048</v>
       </c>
       <c r="H81" t="n">
-        <v>0.03405703487114223</v>
+        <v>0.03406396540397263</v>
       </c>
       <c r="I81" t="n">
-        <v>-2.53110289662303</v>
+        <v>-2.528291612266555</v>
       </c>
       <c r="J81" t="n">
         <v>1</v>
@@ -5124,7 +5124,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S81" t="n">
-        <v>116.9535911896506</v>
+        <v>116.9535914067</v>
       </c>
     </row>
     <row r="82">
@@ -5144,16 +5144,16 @@
         <v>5.954436849899731</v>
       </c>
       <c r="F82" t="n">
-        <v>1.05414972993173</v>
+        <v>1.057301109807646</v>
       </c>
       <c r="G82" t="n">
-        <v>1.143791622752867</v>
+        <v>1.146870582815147</v>
       </c>
       <c r="H82" t="n">
-        <v>0.03986651678390481</v>
+        <v>0.03986198764007297</v>
       </c>
       <c r="I82" t="n">
-        <v>-2.24855091572304</v>
+        <v>-2.246989633739612</v>
       </c>
       <c r="J82" t="n">
         <v>1</v>
@@ -5183,7 +5183,7 @@
         <v>-0.007925036076942837</v>
       </c>
       <c r="S82" t="n">
-        <v>116.0267297601446</v>
+        <v>116.0267299754739</v>
       </c>
     </row>
     <row r="83">
@@ -5203,16 +5203,16 @@
         <v>5.948090365497994</v>
       </c>
       <c r="F83" t="n">
-        <v>1.058814904173736</v>
+        <v>1.061962925178993</v>
       </c>
       <c r="G83" t="n">
-        <v>1.14062719989929</v>
+        <v>1.143712641631447</v>
       </c>
       <c r="H83" t="n">
-        <v>0.04397836467034311</v>
+        <v>0.04396615313593655</v>
       </c>
       <c r="I83" t="n">
-        <v>-1.860285081967242</v>
+        <v>-1.859378422298994</v>
       </c>
       <c r="J83" t="n">
         <v>1</v>
@@ -5242,7 +5242,7 @@
         <v>0.006398133597668098</v>
       </c>
       <c r="S83" t="n">
-        <v>116.7690842780505</v>
+        <v>116.7690844947576</v>
       </c>
     </row>
     <row r="84">
@@ -5262,16 +5262,16 @@
         <v>5.961515828160556</v>
       </c>
       <c r="F84" t="n">
-        <v>1.039239860537966</v>
+        <v>1.0423949869562</v>
       </c>
       <c r="G84" t="n">
-        <v>1.136997337941113</v>
+        <v>1.140089138445227</v>
       </c>
       <c r="H84" t="n">
-        <v>0.04916933114470609</v>
+        <v>0.04914956654961976</v>
       </c>
       <c r="I84" t="n">
-        <v>-1.988179931011161</v>
+        <v>-1.987691008228885</v>
       </c>
       <c r="J84" t="n">
         <v>1</v>
@@ -5301,7 +5301,7 @@
         <v>-0.02357115370730396</v>
       </c>
       <c r="S84" t="n">
-        <v>114.0167022442715</v>
+        <v>114.0167024558705</v>
       </c>
     </row>
     <row r="85">
@@ -5321,16 +5321,16 @@
         <v>5.98595539627007</v>
       </c>
       <c r="F85" t="n">
-        <v>1.077914732991801</v>
+        <v>1.081082794027541</v>
       </c>
       <c r="G85" t="n">
-        <v>1.135550856120482</v>
+        <v>1.138648654121293</v>
       </c>
       <c r="H85" t="n">
-        <v>0.05051031467459768</v>
+        <v>0.05048518728946609</v>
       </c>
       <c r="I85" t="n">
-        <v>-1.141076302929208</v>
+        <v>-1.140252481657399</v>
       </c>
       <c r="J85" t="n">
         <v>1</v>
@@ -5360,7 +5360,7 @@
         <v>0.03283904808881903</v>
       </c>
       <c r="S85" t="n">
-        <v>117.7609022121997</v>
+        <v>117.7609024307474</v>
       </c>
     </row>
     <row r="86">
@@ -5380,16 +5380,16 @@
         <v>5.985829728516112</v>
       </c>
       <c r="F86" t="n">
-        <v>1.095508668442394</v>
+        <v>1.098676662968598</v>
       </c>
       <c r="G86" t="n">
-        <v>1.134614938469444</v>
+        <v>1.137718633252135</v>
       </c>
       <c r="H86" t="n">
-        <v>0.05109624453940078</v>
+        <v>0.05106757427915344</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7653452886717393</v>
+        <v>-0.7645158563850919</v>
       </c>
       <c r="J86" t="n">
         <v>0</v>
@@ -5419,7 +5419,7 @@
         <v>0.01770494882172351</v>
       </c>
       <c r="S86" t="n">
-        <v>119.8458529590666</v>
+        <v>119.8458531814837</v>
       </c>
     </row>
     <row r="87">
@@ -5439,16 +5439,16 @@
         <v>5.992865390419841</v>
       </c>
       <c r="F87" t="n">
-        <v>1.107847236785466</v>
+        <v>1.111018954928848</v>
       </c>
       <c r="G87" t="n">
-        <v>1.132889051030483</v>
+        <v>1.135998932837899</v>
       </c>
       <c r="H87" t="n">
-        <v>0.05140272918670828</v>
+        <v>0.05137302611451877</v>
       </c>
       <c r="I87" t="n">
-        <v>-0.487168962450576</v>
+        <v>-0.4862469626252387</v>
       </c>
       <c r="J87" t="n">
         <v>0</v>
@@ -5478,7 +5478,7 @@
         <v>-7.936507936507937e-05</v>
       </c>
       <c r="S87" t="n">
-        <v>119.836341383435</v>
+        <v>119.8363416058344</v>
       </c>
     </row>
     <row r="88">
@@ -5498,16 +5498,16 @@
         <v>5.962056385069926</v>
       </c>
       <c r="F88" t="n">
-        <v>1.149271818840051</v>
+        <v>1.152427231347499</v>
       </c>
       <c r="G88" t="n">
-        <v>1.133507829321074</v>
+        <v>1.136622745533655</v>
       </c>
       <c r="H88" t="n">
-        <v>0.05152784146295274</v>
+        <v>0.05149913434170444</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3059314939538245</v>
+        <v>0.3068883781420213</v>
       </c>
       <c r="J88" t="n">
         <v>0</v>
@@ -5537,7 +5537,7 @@
         <v>0</v>
       </c>
       <c r="S88" t="n">
-        <v>119.836341383435</v>
+        <v>119.8363416058344</v>
       </c>
     </row>
     <row r="89">
@@ -5557,16 +5557,16 @@
         <v>5.958731556573001</v>
       </c>
       <c r="F89" t="n">
-        <v>1.157724558875872</v>
+        <v>1.160878211721092</v>
       </c>
       <c r="G89" t="n">
-        <v>1.133944163477612</v>
+        <v>1.137063087600154</v>
       </c>
       <c r="H89" t="n">
-        <v>0.05170256594109949</v>
+        <v>0.05167552893739238</v>
       </c>
       <c r="I89" t="n">
-        <v>0.4599461354655137</v>
+        <v>0.4608588360999878</v>
       </c>
       <c r="J89" t="n">
         <v>0</v>
@@ -5596,7 +5596,7 @@
         <v>0</v>
       </c>
       <c r="S89" t="n">
-        <v>119.836341383435</v>
+        <v>119.8363416058344</v>
       </c>
     </row>
     <row r="90">
@@ -5616,16 +5616,16 @@
         <v>5.997396093626087</v>
       </c>
       <c r="F90" t="n">
-        <v>1.152839372287562</v>
+        <v>1.156013488301181</v>
       </c>
       <c r="G90" t="n">
-        <v>1.133986256265999</v>
+        <v>1.1371098789093</v>
       </c>
       <c r="H90" t="n">
-        <v>0.0517183776238547</v>
+        <v>0.05169312004072711</v>
       </c>
       <c r="I90" t="n">
-        <v>0.3645341731073014</v>
+        <v>0.365689077714551</v>
       </c>
       <c r="J90" t="n">
         <v>0</v>
@@ -5655,7 +5655,7 @@
         <v>0</v>
       </c>
       <c r="S90" t="n">
-        <v>119.836341383435</v>
+        <v>119.8363416058344</v>
       </c>
     </row>
     <row r="91">
@@ -5675,16 +5675,16 @@
         <v>5.993538886487244</v>
       </c>
       <c r="F91" t="n">
-        <v>1.198529912309011</v>
+        <v>1.201701986899527</v>
       </c>
       <c r="G91" t="n">
-        <v>1.136327552119506</v>
+        <v>1.139455857700518</v>
       </c>
       <c r="H91" t="n">
-        <v>0.05358876209393353</v>
+        <v>0.05356803063839567</v>
       </c>
       <c r="I91" t="n">
-        <v>1.160735157130024</v>
+        <v>1.16200144857283</v>
       </c>
       <c r="J91" t="n">
         <v>-1</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="S91" t="n">
-        <v>119.836341383435</v>
+        <v>119.8363416058344</v>
       </c>
     </row>
     <row r="92">
@@ -5734,16 +5734,16 @@
         <v>5.982784867071093</v>
       </c>
       <c r="F92" t="n">
-        <v>1.160971065587266</v>
+        <v>1.16413744862353</v>
       </c>
       <c r="G92" t="n">
-        <v>1.136552506832776</v>
+        <v>1.139684768744477</v>
       </c>
       <c r="H92" t="n">
-        <v>0.05368712776772819</v>
+        <v>0.05366814779202046</v>
       </c>
       <c r="I92" t="n">
-        <v>0.4548307903550858</v>
+        <v>0.4556274230631825</v>
       </c>
       <c r="J92" t="n">
         <v>0</v>
@@ -5773,7 +5773,7 @@
         <v>0.03350482553124223</v>
       </c>
       <c r="S92" t="n">
-        <v>123.8514370937893</v>
+        <v>123.8514373236402</v>
       </c>
     </row>
     <row r="93">
@@ -5793,16 +5793,16 @@
         <v>5.983188051122531</v>
       </c>
       <c r="F93" t="n">
-        <v>1.147280472637744</v>
+        <v>1.150447069058773</v>
       </c>
       <c r="G93" t="n">
-        <v>1.135552624641517</v>
+        <v>1.138689185555007</v>
       </c>
       <c r="H93" t="n">
-        <v>0.05326936363834962</v>
+        <v>0.05325225123858657</v>
       </c>
       <c r="I93" t="n">
-        <v>0.2201612182914076</v>
+        <v>0.2207959894706983</v>
       </c>
       <c r="J93" t="n">
         <v>0</v>
@@ -5832,7 +5832,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S93" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="94">
@@ -5852,16 +5852,16 @@
         <v>5.959531545016149</v>
       </c>
       <c r="F94" t="n">
-        <v>1.156385266217722</v>
+        <v>1.159539342456044</v>
       </c>
       <c r="G94" t="n">
-        <v>1.135005503829196</v>
+        <v>1.138146143150917</v>
       </c>
       <c r="H94" t="n">
-        <v>0.05298124533018352</v>
+        <v>0.05296646718855946</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4035345385954198</v>
+        <v>0.403900815755124</v>
       </c>
       <c r="J94" t="n">
         <v>0</v>
@@ -5891,7 +5891,7 @@
         <v>-0</v>
       </c>
       <c r="S94" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="95">
@@ -5911,16 +5911,16 @@
         <v>5.962750867995942</v>
       </c>
       <c r="F95" t="n">
-        <v>1.16697620915135</v>
+        <v>1.170131989213208</v>
       </c>
       <c r="G95" t="n">
-        <v>1.135081340989169</v>
+        <v>1.138225589903656</v>
       </c>
       <c r="H95" t="n">
-        <v>0.05302819604618215</v>
+        <v>0.05301562937180816</v>
       </c>
       <c r="I95" t="n">
-        <v>0.6014699827692328</v>
+        <v>0.6018300581850323</v>
       </c>
       <c r="J95" t="n">
         <v>0</v>
@@ -5950,7 +5950,7 @@
         <v>0</v>
       </c>
       <c r="S95" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="96">
@@ -5970,16 +5970,16 @@
         <v>5.959531545016149</v>
       </c>
       <c r="F96" t="n">
-        <v>1.1513865966574</v>
+        <v>1.154540672895722</v>
       </c>
       <c r="G96" t="n">
-        <v>1.135043808775674</v>
+        <v>1.138191615647709</v>
       </c>
       <c r="H96" t="n">
-        <v>0.05301575307530886</v>
+        <v>0.05300438199305395</v>
       </c>
       <c r="I96" t="n">
-        <v>0.3082628640304559</v>
+        <v>0.3084472761168331</v>
       </c>
       <c r="J96" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         <v>-0</v>
       </c>
       <c r="S96" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="97">
@@ -6029,16 +6029,16 @@
         <v>5.94735954974672</v>
       </c>
       <c r="F97" t="n">
-        <v>1.140818178863733</v>
+        <v>1.143965813085469</v>
       </c>
       <c r="G97" t="n">
-        <v>1.13293545200887</v>
+        <v>1.136086067948005</v>
       </c>
       <c r="H97" t="n">
-        <v>0.05183414006595252</v>
+        <v>0.05182537110077693</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1520759646988046</v>
+        <v>0.1520441623493945</v>
       </c>
       <c r="J97" t="n">
         <v>0</v>
@@ -6068,7 +6068,7 @@
         <v>-0</v>
       </c>
       <c r="S97" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="98">
@@ -6088,16 +6088,16 @@
         <v>5.962673683416126</v>
       </c>
       <c r="F98" t="n">
-        <v>1.127740590995563</v>
+        <v>1.130896330207557</v>
       </c>
       <c r="G98" t="n">
-        <v>1.128818206590366</v>
+        <v>1.131971584328586</v>
       </c>
       <c r="H98" t="n">
-        <v>0.04854981491006437</v>
+        <v>0.04854486077788634</v>
       </c>
       <c r="I98" t="n">
-        <v>-0.02219608039287325</v>
+        <v>-0.02214970037608711</v>
       </c>
       <c r="J98" t="n">
         <v>0</v>
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="S98" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="99">
@@ -6147,16 +6147,16 @@
         <v>5.962545055387006</v>
       </c>
       <c r="F99" t="n">
-        <v>1.117257888946309</v>
+        <v>1.120413560082045</v>
       </c>
       <c r="G99" t="n">
-        <v>1.124920359669364</v>
+        <v>1.12807653813524</v>
       </c>
       <c r="H99" t="n">
-        <v>0.04600107064509103</v>
+        <v>0.04600014104579171</v>
       </c>
       <c r="I99" t="n">
-        <v>-0.166571573565588</v>
+        <v>-0.1665859686292558</v>
       </c>
       <c r="J99" t="n">
         <v>0</v>
@@ -6186,7 +6186,7 @@
         <v>-0</v>
       </c>
       <c r="S99" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="100">
@@ -6206,16 +6206,16 @@
         <v>5.965882922901972</v>
       </c>
       <c r="F100" t="n">
-        <v>1.122614812696884</v>
+        <v>1.125772250395736</v>
       </c>
       <c r="G100" t="n">
-        <v>1.122234636655242</v>
+        <v>1.125393692074393</v>
       </c>
       <c r="H100" t="n">
-        <v>0.04438115325839519</v>
+        <v>0.0443837986477135</v>
       </c>
       <c r="I100" t="n">
-        <v>0.008566159590953464</v>
+        <v>0.008529200583925856</v>
       </c>
       <c r="J100" t="n">
         <v>0</v>
@@ -6245,7 +6245,7 @@
         <v>0</v>
       </c>
       <c r="S100" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="101">
@@ -6265,16 +6265,16 @@
         <v>5.940468433706842</v>
       </c>
       <c r="F101" t="n">
-        <v>1.126069333264446</v>
+        <v>1.129213320369762</v>
       </c>
       <c r="G101" t="n">
-        <v>1.1254670605097</v>
+        <v>1.128625807426249</v>
       </c>
       <c r="H101" t="n">
-        <v>0.04200968951430623</v>
+        <v>0.0420117589952684</v>
       </c>
       <c r="I101" t="n">
-        <v>0.01433652001976859</v>
+        <v>0.01398448809485707</v>
       </c>
       <c r="J101" t="n">
         <v>0</v>
@@ -6304,7 +6304,7 @@
         <v>-0</v>
       </c>
       <c r="S101" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="102">
@@ -6324,16 +6324,16 @@
         <v>5.929975570597685</v>
       </c>
       <c r="F102" t="n">
-        <v>1.19426307010501</v>
+        <v>1.197401503872793</v>
       </c>
       <c r="G102" t="n">
-        <v>1.132472727518364</v>
+        <v>1.135630827129506</v>
       </c>
       <c r="H102" t="n">
-        <v>0.04116501333812039</v>
+        <v>0.04116478304143233</v>
       </c>
       <c r="I102" t="n">
-        <v>1.501040266381391</v>
+        <v>1.500570929309055</v>
       </c>
       <c r="J102" t="n">
         <v>-1</v>
@@ -6363,7 +6363,7 @@
         <v>0</v>
       </c>
       <c r="S102" t="n">
-        <v>123.8612665729238</v>
+        <v>123.8612668027929</v>
       </c>
     </row>
     <row r="103">
@@ -6383,16 +6383,16 @@
         <v>5.890632658072621</v>
       </c>
       <c r="F103" t="n">
-        <v>1.215358934396017</v>
+        <v>1.218476545965846</v>
       </c>
       <c r="G103" t="n">
-        <v>1.140299929029478</v>
+        <v>1.143456508168848</v>
       </c>
       <c r="H103" t="n">
-        <v>0.04130499830860931</v>
+        <v>0.04129985062496552</v>
       </c>
       <c r="I103" t="n">
-        <v>1.817189406612167</v>
+        <v>1.816472376092523</v>
       </c>
       <c r="J103" t="n">
         <v>-1</v>
@@ -6422,7 +6422,7 @@
         <v>-0.03171505863344803</v>
       </c>
       <c r="S103" t="n">
-        <v>119.9329992411504</v>
+        <v>119.9329994637291</v>
       </c>
     </row>
     <row r="104">
@@ -6442,16 +6442,16 @@
         <v>5.882697390434339</v>
       </c>
       <c r="F104" t="n">
-        <v>1.184113344748763</v>
+        <v>1.18722675658596</v>
       </c>
       <c r="G104" t="n">
-        <v>1.147543603240018</v>
+        <v>1.150698096650336</v>
       </c>
       <c r="H104" t="n">
-        <v>0.03484780175225395</v>
+        <v>0.03483907899050148</v>
       </c>
       <c r="I104" t="n">
-        <v>1.04941315290797</v>
+        <v>1.048496716735329</v>
       </c>
       <c r="J104" t="n">
         <v>-1</v>
@@ -6481,7 +6481,7 @@
         <v>0.02839308435229533</v>
       </c>
       <c r="S104" t="n">
-        <v>123.3382670052281</v>
+        <v>123.3382672341266</v>
       </c>
     </row>
     <row r="105">
@@ -6501,16 +6501,16 @@
         <v>5.918807384063352</v>
       </c>
       <c r="F105" t="n">
-        <v>1.177637617228203</v>
+        <v>1.180770140244192</v>
       </c>
       <c r="G105" t="n">
-        <v>1.152529747451838</v>
+        <v>1.155682463961169</v>
       </c>
       <c r="H105" t="n">
-        <v>0.03131609126999332</v>
+        <v>0.03130715923679537</v>
       </c>
       <c r="I105" t="n">
-        <v>0.8017561821459879</v>
+        <v>0.8013399137644338</v>
       </c>
       <c r="J105" t="n">
         <v>0</v>
@@ -6540,7 +6540,7 @@
         <v>0.01745528691344207</v>
       </c>
       <c r="S105" t="n">
-        <v>125.4911718432111</v>
+        <v>125.4911720761051</v>
       </c>
     </row>
     <row r="106">
@@ -6560,16 +6560,16 @@
         <v>5.908924968232186</v>
       </c>
       <c r="F106" t="n">
-        <v>1.120646366389124</v>
+        <v>1.123773659146204</v>
       </c>
       <c r="G106" t="n">
-        <v>1.153786632349175</v>
+        <v>1.156937313770049</v>
       </c>
       <c r="H106" t="n">
-        <v>0.02934980069856702</v>
+        <v>0.02934337878075037</v>
       </c>
       <c r="I106" t="n">
-        <v>-1.129147904628485</v>
+        <v>-1.13019209108942</v>
       </c>
       <c r="J106" t="n">
         <v>1</v>
@@ -6599,7 +6599,7 @@
         <v>7.936507936507937e-05</v>
       </c>
       <c r="S106" t="n">
-        <v>125.5011314600241</v>
+        <v>125.5011316929365</v>
       </c>
     </row>
     <row r="107">
@@ -6619,16 +6619,16 @@
         <v>5.895256457589491</v>
       </c>
       <c r="F107" t="n">
-        <v>1.14748097267776</v>
+        <v>1.150601031388959</v>
       </c>
       <c r="G107" t="n">
-        <v>1.155768319143789</v>
+        <v>1.158916417593055</v>
       </c>
       <c r="H107" t="n">
-        <v>0.02735497342249278</v>
+        <v>0.02735051182436524</v>
       </c>
       <c r="I107" t="n">
-        <v>-0.3029557491441568</v>
+        <v>-0.304030369065639</v>
       </c>
       <c r="J107" t="n">
         <v>0</v>
@@ -6658,7 +6658,7 @@
         <v>0.03083536069553861</v>
       </c>
       <c r="S107" t="n">
-        <v>129.3710041162921</v>
+        <v>129.3710043563865</v>
       </c>
     </row>
     <row r="108">
@@ -6678,16 +6678,16 @@
         <v>5.897867925179888</v>
       </c>
       <c r="F108" t="n">
-        <v>1.143464369789111</v>
+        <v>1.146585810616977</v>
       </c>
       <c r="G108" t="n">
-        <v>1.155477946691243</v>
+        <v>1.158624346556529</v>
       </c>
       <c r="H108" t="n">
-        <v>0.02745819135595296</v>
+        <v>0.02745444807648283</v>
       </c>
       <c r="I108" t="n">
-        <v>-0.4375225136424325</v>
+        <v>-0.4384912749298324</v>
       </c>
       <c r="J108" t="n">
         <v>0</v>
@@ -6717,7 +6717,7 @@
         <v>-7.936507936507937e-05</v>
       </c>
       <c r="S108" t="n">
-        <v>129.3607365762829</v>
+        <v>129.3607368163582</v>
       </c>
     </row>
     <row r="109">
@@ -6737,16 +6737,16 @@
         <v>5.875997591000409</v>
       </c>
       <c r="F109" t="n">
-        <v>1.120984139858534</v>
+        <v>1.124094005833436</v>
       </c>
       <c r="G109" t="n">
-        <v>1.153640925740376</v>
+        <v>1.156785136262146</v>
       </c>
       <c r="H109" t="n">
-        <v>0.02850888661294745</v>
+        <v>0.02850743051486295</v>
       </c>
       <c r="I109" t="n">
-        <v>-1.145494958298751</v>
+        <v>-1.146758225427074</v>
       </c>
       <c r="J109" t="n">
         <v>1</v>
@@ -6776,7 +6776,7 @@
         <v>-0</v>
       </c>
       <c r="S109" t="n">
-        <v>129.3607365762829</v>
+        <v>129.3607368163582</v>
       </c>
     </row>
     <row r="110">
@@ -6796,16 +6796,16 @@
         <v>5.879890291127706</v>
       </c>
       <c r="F110" t="n">
-        <v>1.140175824589031</v>
+        <v>1.143287750771667</v>
       </c>
       <c r="G110" t="n">
-        <v>1.153007748355449</v>
+        <v>1.15614884938567</v>
       </c>
       <c r="H110" t="n">
-        <v>0.02866781056695225</v>
+        <v>0.02866713233630243</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.4476073865651421</v>
+        <v>-0.4486356871390527</v>
       </c>
       <c r="J110" t="n">
         <v>0</v>
@@ -6835,7 +6835,7 @@
         <v>0.01830307136781406</v>
       </c>
       <c r="S110" t="n">
-        <v>131.7284353700315</v>
+        <v>131.728435614501</v>
       </c>
     </row>
     <row r="111">
@@ -6855,16 +6855,16 @@
         <v>5.885214726902118</v>
       </c>
       <c r="F111" t="n">
-        <v>1.137949487161507</v>
+        <v>1.141064231296566</v>
       </c>
       <c r="G111" t="n">
-        <v>1.149978727098074</v>
+        <v>1.153116961605522</v>
       </c>
       <c r="H111" t="n">
-        <v>0.02674047623377018</v>
+        <v>0.02673741272632975</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4498513725561356</v>
+        <v>-0.450781473597384</v>
       </c>
       <c r="J111" t="n">
         <v>0</v>
@@ -6894,7 +6894,7 @@
         <v>-7.936507936507937e-05</v>
       </c>
       <c r="S111" t="n">
-        <v>131.7179807323038</v>
+        <v>131.7179809767538</v>
       </c>
     </row>
     <row r="112">
@@ -6914,16 +6914,16 @@
         <v>5.911744720499765</v>
       </c>
       <c r="F112" t="n">
-        <v>1.153849713653827</v>
+        <v>1.156978498762036</v>
       </c>
       <c r="G112" t="n">
-        <v>1.149622659501402</v>
+        <v>1.152759014112448</v>
       </c>
       <c r="H112" t="n">
-        <v>0.02663360131760112</v>
+        <v>0.02662981446820065</v>
       </c>
       <c r="I112" t="n">
-        <v>0.1587113249169001</v>
+        <v>0.158449645025759</v>
       </c>
       <c r="J112" t="n">
         <v>0</v>
@@ -6953,7 +6953,7 @@
         <v>0</v>
       </c>
       <c r="S112" t="n">
-        <v>131.7179807323038</v>
+        <v>131.7179809767538</v>
       </c>
     </row>
     <row r="113">
@@ -6973,16 +6973,16 @@
         <v>5.9222484364193</v>
       </c>
       <c r="F113" t="n">
-        <v>1.122369593483295</v>
+        <v>1.125503937672876</v>
       </c>
       <c r="G113" t="n">
-        <v>1.148377115543679</v>
+        <v>1.151511857543153</v>
       </c>
       <c r="H113" t="n">
-        <v>0.02732248142851952</v>
+        <v>0.02731895376862573</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.9518726228590999</v>
+        <v>-0.9520100985765022</v>
       </c>
       <c r="J113" t="n">
         <v>0</v>
@@ -7012,7 +7012,7 @@
         <v>0</v>
       </c>
       <c r="S113" t="n">
-        <v>131.7179807323038</v>
+        <v>131.7179809767538</v>
       </c>
     </row>
     <row r="114">
@@ -7020,28 +7020,28 @@
         <v>46190</v>
       </c>
       <c r="B114" t="n">
-        <v>205</v>
+        <v>203.8150024414062</v>
       </c>
       <c r="C114" t="n">
-        <v>362.8299865722656</v>
+        <v>363.4800109863281</v>
       </c>
       <c r="D114" t="n">
-        <v>5.323009979138408</v>
+        <v>5.317212731628869</v>
       </c>
       <c r="E114" t="n">
-        <v>5.893934368001432</v>
+        <v>5.895724305052545</v>
       </c>
       <c r="F114" t="n">
-        <v>1.130821040961587</v>
+        <v>1.126870968134838</v>
       </c>
       <c r="G114" t="n">
-        <v>1.147098904280873</v>
+        <v>1.149878438827093</v>
       </c>
       <c r="H114" t="n">
-        <v>0.02752534777608156</v>
+        <v>0.02778635716735103</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.5913772080812839</v>
+        <v>-0.8280132063978529</v>
       </c>
       <c r="J114" t="n">
         <v>0</v>
@@ -7056,10 +7056,10 @@
         <v>0</v>
       </c>
       <c r="N114" t="n">
-        <v>-0.01161951506464221</v>
+        <v>-0.01733282463347197</v>
       </c>
       <c r="O114" t="n">
-        <v>-0.02791698172199431</v>
+        <v>-0.02617545616522943</v>
       </c>
       <c r="P114" t="n">
         <v>-0</v>
@@ -7071,7 +7071,7 @@
         <v>-0</v>
       </c>
       <c r="S114" t="n">
-        <v>131.7179807323038</v>
+        <v>131.7179809767538</v>
       </c>
     </row>
   </sheetData>
